--- a/vault-dalarna-university/03 IKS/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$H$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -490,32 +490,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BY1047</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IIT</t>
+          <t>IKS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2013-03-14</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Byggteknik</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bärkraftigt byggande och boende</t>
+          <t>Historievetenskaplig litteraturkurs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -525,39 +525,39 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GIK289</t>
+          <t>AHI29R</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IIT</t>
+          <t>IKS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Informatik</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Objektorienterad programmering och problemlösning</t>
+          <t>Historievetenskapens teori och metod</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -567,39 +567,39 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GRY2BR</t>
+          <t>GFI37Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ISLL</t>
+          <t>IKS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2023-12-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ryska</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ryska V: Samtida rysk litteratur och kultur</t>
+          <t>Gud och bevisen: filosofiska argument för och mot Guds existens</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -609,39 +609,39 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GPG3CN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ISLL</t>
+          <t>IKS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kinesiska</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kinesiska I med didaktisk inriktning</t>
+          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -651,14 +651,14 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>GHI3CP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Historievetenskaplig litteraturkurs</t>
+          <t>Undervisning och lärande genom rollspel – inriktning historiedidaktik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AHI29R</t>
+          <t>GRK3CQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -715,17 +715,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Historievetenskapens teori och metod</t>
+          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -735,19 +735,19 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GFI37Z</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2023-12-07</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gud och bevisen: filosofiska argument för och mot Guds existens</t>
+          <t>Mentorsutbildning för en kvalitativ introduktionsperiod</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -776,265 +776,13 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>GIH3AQ</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IDA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>IHV</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2024-02-27</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Styrketräningens teori och praktiska tillämpning</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>GKI3C9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>KIA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ISLL</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Kinesiska</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Kinesiska för affärslivet II</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3C9</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>GPG3CN</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Pedagogiskt arbete</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>GHI3CP</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>HIA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Historia</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Undervisning och lärande genom rollspel – inriktning historiedidaktik</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>GRK3CQ</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>RKA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Religionsvetenskap</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>APG2CC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Pedagogiskt arbete</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Mentorsutbildning för en kvalitativ introduktionsperiod</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:H8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
@@ -1050,18 +798,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$398</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$399</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I398"/>
+  <dimension ref="A1:I399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15726,12 +15726,12 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>ARK29H</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -15741,18 +15741,18 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Didaktik och läroplansteori - KPU</t>
+          <t>Religionsvetenskaplig litteraturkurs</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -15762,14 +15762,14 @@
       </c>
       <c r="I348" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Didaktik och läroplansteori</t>
+          <t>Didaktik och läroplansteori - KPU</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -15805,19 +15805,19 @@
       </c>
       <c r="I349" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -15827,18 +15827,18 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Historievetenskaplig litteraturkurs</t>
+          <t>Didaktik och läroplansteori</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -15848,14 +15848,14 @@
       </c>
       <c r="I350" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>AHI29R</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Historievetenskapens teori och metod</t>
+          <t>Historievetenskaplig litteraturkurs</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -15891,14 +15891,14 @@
       </c>
       <c r="I351" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>GHI37M</t>
+          <t>AHI29R</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -15913,7 +15913,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
@@ -15924,7 +15924,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>De nationella minoriteternas samhällshistoria</t>
+          <t>Historievetenskapens teori och metod</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -15934,19 +15934,19 @@
       </c>
       <c r="I352" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI37M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>GFI37Z</t>
+          <t>GHI37M</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -15956,18 +15956,18 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2023-12-07</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Gud och bevisen: filosofiska argument för och mot Guds existens</t>
+          <t>De nationella minoriteternas samhällshistoria</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -15977,19 +15977,19 @@
       </c>
       <c r="I353" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI37M</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>GHI38Q</t>
+          <t>GFI37Z</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -15999,18 +15999,18 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-12-07</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Global miljöhistoria</t>
+          <t>Gud och bevisen: filosofiska argument för och mot Guds existens</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -16020,19 +16020,19 @@
       </c>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI38Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>GBQ38X</t>
+          <t>GHI38Q</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -16042,18 +16042,18 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Fortsätt berätta med film om kulturarv och historia</t>
+          <t>Global miljöhistoria</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -16063,19 +16063,19 @@
       </c>
       <c r="I355" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI38Q</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>GEU38C</t>
+          <t>GBQ38X</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -16085,18 +16085,18 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>Fortsätt berätta med film om kulturarv och historia</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -16106,19 +16106,19 @@
       </c>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU38C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>APG2AA</t>
+          <t>GEU38C</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -16128,18 +16128,18 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Lärarskicklighet - utveckling av lärarskicklighet i förskola och skola utifrån forskning</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -16149,19 +16149,19 @@
       </c>
       <c r="I357" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU38C</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A5</t>
+          <t>APG2AA</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -16171,18 +16171,18 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Grunderna i filmproduktion</t>
+          <t>Lärarskicklighet - utveckling av lärarskicklighet i förskola och skola utifrån forskning</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -16192,14 +16192,14 @@
       </c>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A6</t>
+          <t>GBQ3A5</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Konceptutveckling för korta filmer</t>
+          <t>Grunderna i filmproduktion</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -16235,14 +16235,14 @@
       </c>
       <c r="I359" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A5</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A7</t>
+          <t>GBQ3A6</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Star Wars: Film, myter och världar</t>
+          <t>Konceptutveckling för korta filmer</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -16278,14 +16278,14 @@
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A8</t>
+          <t>GBQ3A7</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Kreativt skrivande</t>
+          <t>Star Wars: Film, myter och världar</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -16321,14 +16321,14 @@
       </c>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A9</t>
+          <t>GBQ3A8</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Introduktion till att skriva filmadaption</t>
+          <t>Kreativt skrivande</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -16364,14 +16364,14 @@
       </c>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A8</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AA</t>
+          <t>GBQ3A9</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Filmhistoria: En introduktion</t>
+          <t>Introduktion till att skriva filmadaption</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -16407,19 +16407,19 @@
       </c>
       <c r="I363" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A9</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>GTR3A4</t>
+          <t>GBQ3AA</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -16435,12 +16435,12 @@
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Kvantitativ metod</t>
+          <t>Filmhistoria: En introduktion</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -16450,19 +16450,19 @@
       </c>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>APG2AB</t>
+          <t>GTR3A4</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -16472,18 +16472,18 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL</t>
+          <t>Kvantitativ metod</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -16493,14 +16493,14 @@
       </c>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>APG2AB</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -16526,7 +16526,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Rektors pedagogiska ledarskap med fokus på förskolans utbildningsuppdrag</t>
+          <t>Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -16536,14 +16536,14 @@
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AB</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>GPG3AD</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 1 för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Rektors pedagogiska ledarskap med fokus på förskolans utbildningsuppdrag</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -16579,14 +16579,14 @@
       </c>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>GPG3AF</t>
+          <t>GPG3AD</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Specialpedagogik och ett läraruppdrag i förändring för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Verksamhetsförlagd utbildning 1 för ämneslärare årskurs 7–9 - AIL</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -16622,14 +16622,14 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>GPG3AG</t>
+          <t>GPG3AF</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -16655,7 +16655,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 2 för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Specialpedagogik och ett läraruppdrag i förändring för ämneslärare årskurs 7–9 - AIL</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -16665,19 +16665,19 @@
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>GPG3AG</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -16687,18 +16687,18 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Hårdrock och metal: musikproduktion, kultur och kreativa konventioner</t>
+          <t>Verksamhetsförlagd utbildning 2 för ämneslärare årskurs 7–9 - AIL</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -16708,19 +16708,19 @@
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>GAB3AK</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -16730,18 +16730,18 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Kommunal styrning och förändringsarbete</t>
+          <t>Hårdrock och metal: musikproduktion, kultur och kreativa konventioner</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -16751,14 +16751,14 @@
       </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>GAB3AL</t>
+          <t>GAB3AK</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Ledarskapets juridik</t>
+          <t>Kommunal styrning och förändringsarbete</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -16794,19 +16794,19 @@
       </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AK</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>GLP3AR</t>
+          <t>GAB3AL</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -16816,18 +16816,18 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion med Pro Tools</t>
+          <t>Ledarskapets juridik</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -16837,19 +16837,19 @@
       </c>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AL</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AV</t>
+          <t>GLP3AR</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -16859,18 +16859,18 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Content för sociala medier</t>
+          <t>Ljud- och musikproduktion med Pro Tools</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -16880,14 +16880,14 @@
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AW</t>
+          <t>GBQ3AV</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Explainers med rörlig grafik</t>
+          <t>Content för sociala medier</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -16923,19 +16923,19 @@
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>GTR3B6</t>
+          <t>GBQ3AW</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -16945,18 +16945,18 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Sälenfjällen - Platsen och besöksnäringen</t>
+          <t>Explainers med rörlig grafik</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -16966,19 +16966,19 @@
       </c>
       <c r="I376" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>GNA3B7</t>
+          <t>GTR3B6</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -16988,18 +16988,18 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Nationalekonomi</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Mikroekonomi, introduktion</t>
+          <t>Sälenfjällen - Platsen och besöksnäringen</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -17009,19 +17009,19 @@
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>GBP3BB</t>
+          <t>GNA3B7</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -17031,18 +17031,18 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Nationalekonomi</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Fotografiskt bildskapande A</t>
+          <t>Mikroekonomi, introduktion</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -17052,14 +17052,14 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B7</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>GBP3BC</t>
+          <t>GBP3BB</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Fotografiskt bildskapande B</t>
+          <t>Fotografiskt bildskapande A</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -17095,19 +17095,19 @@
       </c>
       <c r="I379" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BB</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>GPG3BD</t>
+          <t>GBP3BC</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -17123,12 +17123,12 @@
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Introduktion till läraryrket</t>
+          <t>Fotografiskt bildskapande B</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -17138,19 +17138,19 @@
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BC</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>GFI3BU</t>
+          <t>GPG3BD</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -17160,18 +17160,18 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Introduktion till existentialismen</t>
+          <t>Introduktion till läraryrket</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -17181,19 +17181,19 @@
       </c>
       <c r="I381" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>ABQ2AM</t>
+          <t>GFI3BU</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -17203,18 +17203,18 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Kreativ kodning</t>
+          <t>Introduktion till existentialismen</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -17224,19 +17224,19 @@
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>GPG3CN</t>
+          <t>ABQ2AM</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -17246,18 +17246,18 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
+          <t>Kreativ kodning</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -17267,19 +17267,19 @@
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>GHI3CP</t>
+          <t>GPG3CN</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -17289,18 +17289,18 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel – inriktning historiedidaktik</t>
+          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -17310,19 +17310,19 @@
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>GRK3CQ</t>
+          <t>GHI3CP</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -17338,12 +17338,12 @@
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
+          <t>Undervisning och lärande genom rollspel – inriktning historiedidaktik</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -17353,19 +17353,19 @@
       </c>
       <c r="I385" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>GMN3E2</t>
+          <t>GRK3CQ</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -17375,18 +17375,18 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Dramaturgi, manusskrivande och medieproduktionens villkor</t>
+          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -17396,14 +17396,14 @@
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>GMN3EZ</t>
+          <t>GMN3E2</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -17418,7 +17418,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -17429,7 +17429,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Kandidatexamensarbete i Medieproduktion</t>
+          <t>Dramaturgi, manusskrivande och medieproduktionens villkor</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -17439,14 +17439,14 @@
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E2</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>GMN3EX</t>
+          <t>GMN3EZ</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Alternativa gestaltningsformer</t>
+          <t>Kandidatexamensarbete i Medieproduktion</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -17482,14 +17482,14 @@
       </c>
       <c r="I388" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>GMN3EY</t>
+          <t>GMN3EX</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -17515,7 +17515,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Vetenskapsteori och metod i Medieproduktion</t>
+          <t>Alternativa gestaltningsformer</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -17525,14 +17525,14 @@
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>GMN3F2</t>
+          <t>GMN3EY</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Exponeringsprojekt inom Medieproduktion</t>
+          <t>Vetenskapsteori och metod i Medieproduktion</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -17568,19 +17568,19 @@
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EY</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>GBQ3FG</t>
+          <t>GMN3F2</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -17590,18 +17590,18 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Kreativt skrivande</t>
+          <t>Exponeringsprojekt inom Medieproduktion</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -17611,19 +17611,19 @@
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>APG2BF</t>
+          <t>GBQ3FG</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -17639,12 +17639,12 @@
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Att främja en professionsdriven verksamhetsutveckling i förskola, skola och fritidshem</t>
+          <t>Kreativt skrivande</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -17654,14 +17654,14 @@
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>APG2BK</t>
+          <t>APG2BF</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
@@ -17687,7 +17687,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 3 - VAL</t>
+          <t>Att främja en professionsdriven verksamhetsutveckling i förskola, skola och fritidshem</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -17697,14 +17697,14 @@
       </c>
       <c r="I393" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>APG2BK</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -17730,7 +17730,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Introduktion till studier i program - VAL</t>
+          <t>Verksamhetsförlagd utbildning 3 - VAL</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -17740,14 +17740,14 @@
       </c>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>GPG3FS</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 1 - VAL</t>
+          <t>Introduktion till studier i program - VAL</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -17783,14 +17783,14 @@
       </c>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>GPG3FT</t>
+          <t>GPG3FS</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 2 - VAL</t>
+          <t>Verksamhetsförlagd utbildning 1 - VAL</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -17826,19 +17826,19 @@
       </c>
       <c r="I396" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>GMN3F3</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -17848,18 +17848,18 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning inom medieproduktion</t>
+          <t>Verksamhetsförlagd utbildning 2 - VAL</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -17869,19 +17869,19 @@
       </c>
       <c r="I397" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>GMN3F3</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -17891,33 +17891,76 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr">
         <is>
+          <t>Medieproduktion</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Verksamhetsförlagd utbildning inom medieproduktion</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>APG2CC</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>IKS</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr"/>
+      <c r="F399" t="inlineStr">
+        <is>
           <t>Pedagogiskt arbete</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr">
+      <c r="G399" t="inlineStr">
         <is>
           <t>Mentorsutbildning för en kvalitativ introduktionsperiod</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I398" s="2" t="inlineStr">
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I398"/>
+  <autoFilter ref="A1:I399"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -18713,6 +18756,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I397" r:id="rId792"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A398" r:id="rId793"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I398" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A399" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I399" r:id="rId796"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$425</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$427</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I425"/>
+  <dimension ref="A1:I427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14252,12 +14252,12 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GLP2QC</t>
+          <t>FPA222F</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -14267,18 +14267,18 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-04</t>
         </is>
       </c>
       <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Projektarbete inom medieproduktion, fördjupningskurs</t>
+          <t>Akademiskt skrivande och talande på engelska</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -14288,19 +14288,19 @@
       </c>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222F</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>GLP2QD</t>
+          <t>FPA222G</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -14310,18 +14310,18 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-04</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Arbetsplatsförlagd utbildning i medieproduktion</t>
+          <t>Forskningskommunikation för samhällsutveckling</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -14331,14 +14331,14 @@
       </c>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>GLP2QU</t>
+          <t>GLP2QC</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Inspelning i studio</t>
+          <t>Projektarbete inom medieproduktion, fördjupningskurs</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -14374,19 +14374,19 @@
       </c>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QC</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>GLP2QD</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -14396,18 +14396,18 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Religionsvetenskap III: Uppsats</t>
+          <t>Arbetsplatsförlagd utbildning i medieproduktion</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -14417,19 +14417,19 @@
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QD</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>GLP2QU</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -14439,18 +14439,18 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Religionsvetenskap III: Examensarbete för kandidatexamen</t>
+          <t>Inspelning i studio</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -14460,19 +14460,19 @@
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QU</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -14482,22 +14482,18 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2010-10-19</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
           <t>2021-09-07</t>
         </is>
       </c>
+      <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Sociologi</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Introduktion till samhällsvetenskap</t>
+          <t>Religionsvetenskap III: Uppsats</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -14507,19 +14503,19 @@
       </c>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>GNA2RY</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -14529,18 +14525,18 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Nationalekonomi</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Statistik för ekonomer</t>
+          <t>Religionsvetenskap III: Examensarbete för kandidatexamen</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -14550,19 +14546,19 @@
       </c>
       <c r="I320" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2RY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>GAB2S5</t>
+          <t>SO1019</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -14572,18 +14568,22 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr"/>
+          <t>2010-10-19</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Sociologi</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Arbetsmiljö</t>
+          <t>Introduktion till samhällsvetenskap</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -14593,19 +14593,19 @@
       </c>
       <c r="I321" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2S5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>GPE2SA</t>
+          <t>GNA2RY</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -14615,18 +14615,18 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2021-12-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Pedagogik</t>
+          <t>Nationalekonomi</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Utbildningssystemet i Sverige</t>
+          <t>Statistik för ekonomer</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -14636,19 +14636,19 @@
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE2SA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2RY</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GAB2S5</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -14658,18 +14658,18 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2021-12-03</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Samhällsorienterande ämnen, årskurs 4-6</t>
+          <t>Arbetsmiljö</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -14679,19 +14679,19 @@
       </c>
       <c r="I323" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2S5</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>GAB2TR</t>
+          <t>GPE2SA</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -14701,18 +14701,18 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2021-12-07</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Pedagogik</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Förståelse och förhållningssätt för främjande av utvecklingsprocesser</t>
+          <t>Utbildningssystemet i Sverige</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -14722,14 +14722,14 @@
       </c>
       <c r="I324" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2TR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE2SA</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>GPG2SG</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="E325" t="inlineStr"/>
@@ -14755,7 +14755,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Omsorg, relationer och etik i förskolläraryrket</t>
+          <t>Samhällsorienterande ämnen, årskurs 4-6</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -14765,19 +14765,19 @@
       </c>
       <c r="I325" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>GPG2SH</t>
+          <t>GAB2TR</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -14787,18 +14787,18 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-07</t>
         </is>
       </c>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Lek i förskolan (varav 7,5 hp VFU)</t>
+          <t>Förståelse och förhållningssätt för främjande av utvecklingsprocesser</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -14808,14 +14808,14 @@
       </c>
       <c r="I326" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2TR</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>GPG2TT</t>
+          <t>GPG2SG</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2021-12-22</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="E327" t="inlineStr"/>
@@ -14851,19 +14851,19 @@
       </c>
       <c r="I327" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U3</t>
+          <t>GPG2SH</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -14873,18 +14873,18 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Människan och den rörliga bilden</t>
+          <t>Lek i förskolan (varav 7,5 hp VFU)</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -14894,19 +14894,19 @@
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U4</t>
+          <t>GPG2TT</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -14916,18 +14916,18 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Informationsfilmsproduktion</t>
+          <t>Omsorg, relationer och etik i förskolläraryrket</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -14937,14 +14937,14 @@
       </c>
       <c r="I329" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U5</t>
+          <t>GBQ2U3</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Kvalificerad filmdesign i transmedia</t>
+          <t>Människan och den rörliga bilden</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -14980,14 +14980,14 @@
       </c>
       <c r="I330" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U3</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U6</t>
+          <t>GBQ2U4</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -15013,7 +15013,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Projektplanering och användarperspektiv</t>
+          <t>Informationsfilmsproduktion</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -15023,14 +15023,14 @@
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U4</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U7</t>
+          <t>GBQ2U5</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Tillämpad filmdesign 1</t>
+          <t>Kvalificerad filmdesign i transmedia</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -15066,14 +15066,14 @@
       </c>
       <c r="I332" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U5</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U8</t>
+          <t>GBQ2U6</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Den korta filmens berättarstruktur</t>
+          <t>Projektplanering och användarperspektiv</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -15109,19 +15109,19 @@
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>GBQ2U7</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -15137,12 +15137,12 @@
       <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Kvinnor och gudinnor på gränsen till den äldsta förhistorien</t>
+          <t>Tillämpad filmdesign 1</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -15152,14 +15152,14 @@
       </c>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U7</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>GBQ2UB</t>
+          <t>GBQ2U8</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="E335" t="inlineStr"/>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Introduktion till produktion av rörlig bild</t>
+          <t>Den korta filmens berättarstruktur</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -15195,19 +15195,19 @@
       </c>
       <c r="I335" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U8</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>GLP2UG</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -15217,18 +15217,18 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Ljudskapande till rörliga bilder</t>
+          <t>Kvinnor och gudinnor på gränsen till den äldsta förhistorien</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -15238,14 +15238,14 @@
       </c>
       <c r="I336" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2UG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>GBQ2UN</t>
+          <t>GBQ2UB</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2022-02-07</t>
         </is>
       </c>
       <c r="E337" t="inlineStr"/>
@@ -15271,7 +15271,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Filmanalys och gestaltning</t>
+          <t>Introduktion till produktion av rörlig bild</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -15281,19 +15281,19 @@
       </c>
       <c r="I337" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>GLP2UG</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -15303,18 +15303,18 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Naturbaserad turism</t>
+          <t>Ljudskapande till rörliga bilder</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -15324,19 +15324,19 @@
       </c>
       <c r="I338" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2UG</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>GBQ2UN</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -15346,18 +15346,18 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Rektors ledning och organisering för utveckling av barns och elevers lärandemiljö</t>
+          <t>Filmanalys och gestaltning</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -15367,19 +15367,19 @@
       </c>
       <c r="I339" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UN</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>APG27U</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -15389,18 +15389,18 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Utvärdering och verksamhetsutveckling i förskola och förskoleklass (varav 7,5 hp VFU)</t>
+          <t>Naturbaserad turism</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -15410,19 +15410,19 @@
       </c>
       <c r="I340" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>GLP2VS</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -15432,18 +15432,18 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2022-03-09</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Arbetsplatsförlagd utbildning i medieproduktion</t>
+          <t>Rektors ledning och organisering för utveckling av barns och elevers lärandemiljö</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -15453,19 +15453,19 @@
       </c>
       <c r="I341" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>GLP2VT</t>
+          <t>APG27U</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -15475,18 +15475,18 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Produktionsprocesser inom musikproduktion</t>
+          <t>Utvärdering och verksamhetsutveckling i förskola och förskoleklass (varav 7,5 hp VFU)</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -15496,19 +15496,19 @@
       </c>
       <c r="I342" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GLP2VS</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -15518,18 +15518,18 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2022-03-15</t>
+          <t>2022-03-09</t>
         </is>
       </c>
       <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Professionellt lärarskap och skolutveckling (varav 10 hp VFU)</t>
+          <t>Arbetsplatsförlagd utbildning i medieproduktion</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -15539,14 +15539,14 @@
       </c>
       <c r="I343" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VS</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>GLP2WB</t>
+          <t>GLP2VT</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="E344" t="inlineStr"/>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Liveljud och liveinspelning</t>
+          <t>Produktionsprocesser inom musikproduktion</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -15582,19 +15582,19 @@
       </c>
       <c r="I344" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>GLP2WC</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -15604,18 +15604,18 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
+          <t>2022-03-15</t>
         </is>
       </c>
       <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Projektarbete inom medieproduktion, fördjupningskurs</t>
+          <t>Professionellt lärarskap och skolutveckling (varav 10 hp VFU)</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -15625,19 +15625,19 @@
       </c>
       <c r="I345" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WG</t>
+          <t>GLP2WB</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -15647,18 +15647,18 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Audiovisuell information och etik</t>
+          <t>Liveljud och liveinspelning</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -15668,19 +15668,19 @@
       </c>
       <c r="I346" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WB</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WH</t>
+          <t>GLP2WC</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -15690,18 +15690,18 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Tillämpad filmdesign 2</t>
+          <t>Projektarbete inom medieproduktion, fördjupningskurs</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -15711,14 +15711,14 @@
       </c>
       <c r="I347" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WC</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WJ</t>
+          <t>GBQ2WG</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -15744,7 +15744,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Reklamfilmsproduktion</t>
+          <t>Audiovisuell information och etik</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -15754,14 +15754,14 @@
       </c>
       <c r="I348" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WG</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WK</t>
+          <t>GBQ2WH</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -15787,7 +15787,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Ljussättning och färgkorrigering inom filmdesign</t>
+          <t>Tillämpad filmdesign 2</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -15797,19 +15797,19 @@
       </c>
       <c r="I349" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>GFÖ2WN</t>
+          <t>GBQ2WJ</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -15819,18 +15819,18 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Redovisning B</t>
+          <t>Reklamfilmsproduktion</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -15840,19 +15840,19 @@
       </c>
       <c r="I350" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ2WN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WJ</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>GBQ2WK</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -15862,18 +15862,18 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)</t>
+          <t>Ljussättning och färgkorrigering inom filmdesign</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -15883,19 +15883,19 @@
       </c>
       <c r="I351" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>GBQ2XC</t>
+          <t>GFÖ2WN</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -15905,18 +15905,18 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Manus för TV och film 3. Dialog i audiovisuella medier</t>
+          <t>Redovisning B</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -15926,19 +15926,19 @@
       </c>
       <c r="I352" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2XC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ2WN</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>GBQ2XD</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -15948,18 +15948,18 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Ljudinspelning och ljudläggning inom filmdesign</t>
+          <t>Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -15969,19 +15969,19 @@
       </c>
       <c r="I353" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2XD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>FPA222J</t>
+          <t>GBQ2XC</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -15991,18 +15991,18 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Grundläggande statistik för utbildningsvetenskaplig forskning</t>
+          <t>Manus för TV och film 3. Dialog i audiovisuella medier</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -16012,19 +16012,19 @@
       </c>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2XC</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>FPA222N</t>
+          <t>GBQ2XD</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -16034,18 +16034,18 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Vetenskapliga metoder för forskning i pedagogiskt arbete</t>
+          <t>Ljudinspelning och ljudläggning inom filmdesign</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -16055,19 +16055,19 @@
       </c>
       <c r="I355" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2XD</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>FPA222J</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -16077,7 +16077,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
@@ -16088,7 +16088,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning för lärare (KPU)</t>
+          <t>Grundläggande statistik för utbildningsvetenskaplig forskning</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -16098,19 +16098,19 @@
       </c>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>FPA222N</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
@@ -16131,7 +16131,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning för lärare (YRK)</t>
+          <t>Vetenskapliga metoder för forskning i pedagogiskt arbete</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -16141,19 +16141,19 @@
       </c>
       <c r="I357" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>GRK323</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -16163,18 +16163,18 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Jerusalem som religiöst, historiskt och politiskt konfliktfylld plats. Berättelser ur ämnesdidaktiska perspektiv</t>
+          <t>Verksamhetsförlagd utbildning för lärare (KPU)</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -16184,19 +16184,19 @@
       </c>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>GHI32G</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -16206,18 +16206,18 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Historia II med didaktisk inriktning</t>
+          <t>Verksamhetsförlagd utbildning för lärare (YRK)</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -16227,19 +16227,19 @@
       </c>
       <c r="I359" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI32G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>GPA32D</t>
+          <t>GRK323</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -16249,18 +16249,18 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Individuella lärprocesser och kompetensutveckling</t>
+          <t>Jerusalem som religiöst, historiskt och politiskt konfliktfylld plats. Berättelser ur ämnesdidaktiska perspektiv</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -16270,19 +16270,19 @@
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>GLP33C</t>
+          <t>GHI32G</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -16292,18 +16292,18 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2023-02-24</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Audiovisuell produktion för pedagogisk verksamhet</t>
+          <t>Historia II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -16313,19 +16313,19 @@
       </c>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP33C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI32G</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>GPA32D</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -16335,22 +16335,18 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
-        </is>
-      </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Afrikanska studier</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Utbildning och förändring i afrikanska samhällen</t>
+          <t>Individuella lärprocesser och kompetensutveckling</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -16360,19 +16356,19 @@
       </c>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>GLP33C</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -16382,22 +16378,18 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
-        </is>
-      </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
+          <t>2023-02-24</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Afrikanska studier</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Afrikanska samhällen i förändring</t>
+          <t>Audiovisuell produktion för pedagogisk verksamhet</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -16407,14 +16399,14 @@
       </c>
       <c r="I363" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP33C</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>AS3001</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -16444,7 +16436,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Religion och politik i afrikanska samhällen</t>
+          <t>Afrikanska studier: Utbildning och förändring i afrikanska samhällen</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -16454,14 +16446,14 @@
       </c>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>AS3004</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -16476,7 +16468,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2015-06-17</t>
+          <t>2014-12-10</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -16491,7 +16483,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Forskningsprojektets planering</t>
+          <t>Afrikanska studier: Afrikanska samhällen i förändring</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -16501,19 +16493,19 @@
       </c>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -16523,18 +16515,22 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
-        </is>
-      </c>
-      <c r="E366" t="inlineStr"/>
+          <t>2014-12-10</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Sociologi</t>
+          <t>Afrikanska studier</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Sociologi III</t>
+          <t>Afrikanska studier: Religion och politik i afrikanska samhällen</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -16544,19 +16540,19 @@
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>GAB358</t>
+          <t>AS3004</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -16566,18 +16562,22 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
-        </is>
-      </c>
-      <c r="E367" t="inlineStr"/>
+          <t>2015-06-17</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Afrikanska studier</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Styrsystem och utveckling i socialtjänst/omsorg</t>
+          <t>Afrikanska studier: Forskningsprojektets planering</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -16587,19 +16587,19 @@
       </c>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB358</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>GLP359</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -16609,18 +16609,18 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Sociologi</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Dansmusikhistoria och klubbkultur 1: DJ-kulturens utveckling 1970-2000</t>
+          <t>Sociologi III</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -16630,19 +16630,19 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>GFÖ35J</t>
+          <t>GAB358</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -16652,18 +16652,18 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Turismmarknadsföring</t>
+          <t>Styrsystem och utveckling i socialtjänst/omsorg</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -16673,19 +16673,19 @@
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ35J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB358</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>GBQ35K</t>
+          <t>GLP359</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -16695,18 +16695,18 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Berätta med film om kulturarv och historia</t>
+          <t>Dansmusikhistoria och klubbkultur 1: DJ-kulturens utveckling 1970-2000</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -16716,19 +16716,19 @@
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ35K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>GEU35M</t>
+          <t>GFÖ35J</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -16738,18 +16738,18 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Entreprenörskap - villkor och särart</t>
+          <t>Turismmarknadsföring</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -16759,19 +16759,19 @@
       </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ35J</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>GEU35N</t>
+          <t>GBQ35K</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -16781,18 +16781,18 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Projektledning II</t>
+          <t>Berätta med film om kulturarv och historia</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -16802,19 +16802,19 @@
       </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ35K</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>ARK29H</t>
+          <t>GEU35M</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -16824,18 +16824,18 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Religionsvetenskaplig litteraturkurs</t>
+          <t>Entreprenörskap - villkor och särart</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -16845,19 +16845,19 @@
       </c>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35M</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GEU35N</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -16867,18 +16867,18 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Didaktik och läroplansteori - KPU</t>
+          <t>Projektledning II</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -16888,19 +16888,19 @@
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35N</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>ARK29H</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -16910,18 +16910,18 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Didaktik och läroplansteori</t>
+          <t>Religionsvetenskaplig litteraturkurs</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -16931,19 +16931,19 @@
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -16953,18 +16953,18 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Historievetenskaplig litteraturkurs</t>
+          <t>Didaktik och läroplansteori - KPU</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -16974,19 +16974,19 @@
       </c>
       <c r="I376" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>AHI29R</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -16996,18 +16996,18 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Historievetenskapens teori och metod</t>
+          <t>Didaktik och läroplansteori</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -17017,14 +17017,14 @@
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>GHI37M</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
@@ -17050,7 +17050,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>De nationella minoriteternas samhällshistoria</t>
+          <t>Historievetenskaplig litteraturkurs</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -17060,19 +17060,19 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI37M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>GFI37Z</t>
+          <t>AHI29R</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -17082,18 +17082,18 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2023-12-07</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Gud och bevisen: filosofiska argument för och mot Guds existens</t>
+          <t>Historievetenskapens teori och metod</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -17103,14 +17103,14 @@
       </c>
       <c r="I379" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>GHI38Q</t>
+          <t>GHI37M</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -17125,7 +17125,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Global miljöhistoria</t>
+          <t>De nationella minoriteternas samhällshistoria</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -17146,19 +17146,19 @@
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI38Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI37M</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>GBQ38X</t>
+          <t>GFI37Z</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -17168,18 +17168,18 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-07</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Fortsätt berätta med film om kulturarv och historia</t>
+          <t>Gud och bevisen: filosofiska argument för och mot Guds existens</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -17189,19 +17189,19 @@
       </c>
       <c r="I381" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>GEU38C</t>
+          <t>GHI38Q</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -17211,18 +17211,18 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>Global miljöhistoria</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -17232,19 +17232,19 @@
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU38C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI38Q</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>APG2AA</t>
+          <t>GBQ38X</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -17254,18 +17254,18 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Lärarskicklighet - utveckling av lärarskicklighet i förskola och skola utifrån forskning</t>
+          <t>Fortsätt berätta med film om kulturarv och historia</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -17275,19 +17275,19 @@
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>GFÖ39A</t>
+          <t>GEU38C</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -17297,18 +17297,18 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Sport Management III</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -17318,19 +17318,19 @@
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ39A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU38C</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A5</t>
+          <t>APG2AA</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -17340,18 +17340,18 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Grunderna i filmproduktion</t>
+          <t>Lärarskicklighet - utveckling av lärarskicklighet i förskola och skola utifrån forskning</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -17361,19 +17361,19 @@
       </c>
       <c r="I385" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A6</t>
+          <t>GFÖ39A</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -17383,18 +17383,18 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Konceptutveckling för korta filmer</t>
+          <t>Sport Management III</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -17404,14 +17404,14 @@
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ39A</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A7</t>
+          <t>GBQ3A5</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Star Wars: Film, myter och världar</t>
+          <t>Grunderna i filmproduktion</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -17447,14 +17447,14 @@
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A5</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A8</t>
+          <t>GBQ3A6</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Kreativt skrivande</t>
+          <t>Konceptutveckling för korta filmer</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -17490,14 +17490,14 @@
       </c>
       <c r="I388" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A9</t>
+          <t>GBQ3A7</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Introduktion till att skriva filmadaption</t>
+          <t>Star Wars: Film, myter och världar</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -17533,14 +17533,14 @@
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AA</t>
+          <t>GBQ3A8</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -17566,7 +17566,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Filmhistoria: En introduktion</t>
+          <t>Kreativt skrivande</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -17576,19 +17576,19 @@
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A8</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>GTR3A4</t>
+          <t>GBQ3A9</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -17604,12 +17604,12 @@
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Kvantitativ metod</t>
+          <t>Introduktion till att skriva filmadaption</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -17619,19 +17619,19 @@
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A9</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>APG2AB</t>
+          <t>GBQ3AA</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -17641,18 +17641,18 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL</t>
+          <t>Filmhistoria: En introduktion</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -17662,19 +17662,19 @@
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>GTR3A4</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -17684,18 +17684,18 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Rektors pedagogiska ledarskap med fokus på förskolans utbildningsuppdrag</t>
+          <t>Kvantitativ metod</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -17705,14 +17705,14 @@
       </c>
       <c r="I393" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>GPG3AD</t>
+          <t>APG2AB</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 1 för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -17748,14 +17748,14 @@
       </c>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AB</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>GPG3AF</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Specialpedagogik och ett läraruppdrag i förändring för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Rektors pedagogiska ledarskap med fokus på förskolans utbildningsuppdrag</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -17791,14 +17791,14 @@
       </c>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>GPG3AG</t>
+          <t>GPG3AD</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -17824,7 +17824,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 2 för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Verksamhetsförlagd utbildning 1 för ämneslärare årskurs 7–9 - AIL</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -17834,19 +17834,19 @@
       </c>
       <c r="I396" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>GPG3AF</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -17856,18 +17856,18 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Hårdrock och metal: musikproduktion, kultur och kreativa konventioner</t>
+          <t>Specialpedagogik och ett läraruppdrag i förändring för ämneslärare årskurs 7–9 - AIL</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -17877,19 +17877,19 @@
       </c>
       <c r="I397" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>GAB3AK</t>
+          <t>GPG3AG</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -17899,18 +17899,18 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Kommunal styrning och förändringsarbete</t>
+          <t>Verksamhetsförlagd utbildning 2 för ämneslärare årskurs 7–9 - AIL</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -17920,19 +17920,19 @@
       </c>
       <c r="I398" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>GAB3AL</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -17942,18 +17942,18 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Ledarskapets juridik</t>
+          <t>Hårdrock och metal: musikproduktion, kultur och kreativa konventioner</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -17963,19 +17963,19 @@
       </c>
       <c r="I399" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>GLP3AR</t>
+          <t>GAB3AK</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -17985,18 +17985,18 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion med Pro Tools</t>
+          <t>Kommunal styrning och förändringsarbete</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -18006,19 +18006,19 @@
       </c>
       <c r="I400" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AK</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AV</t>
+          <t>GAB3AL</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -18028,18 +18028,18 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Content för sociala medier</t>
+          <t>Ledarskapets juridik</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -18049,19 +18049,19 @@
       </c>
       <c r="I401" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AL</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AW</t>
+          <t>GLP3AR</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -18071,18 +18071,18 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Explainers med rörlig grafik</t>
+          <t>Ljud- och musikproduktion med Pro Tools</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -18092,19 +18092,19 @@
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>GTR3B6</t>
+          <t>GBQ3AV</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -18114,18 +18114,18 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Sälenfjällen - Platsen och besöksnäringen</t>
+          <t>Content för sociala medier</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -18135,19 +18135,19 @@
       </c>
       <c r="I403" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>GNA3B7</t>
+          <t>GBQ3AW</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -18157,18 +18157,18 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Nationalekonomi</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Mikroekonomi, introduktion</t>
+          <t>Explainers med rörlig grafik</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -18178,19 +18178,19 @@
       </c>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>GBP3BB</t>
+          <t>GTR3B6</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -18200,18 +18200,18 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Fotografiskt bildskapande A</t>
+          <t>Sälenfjällen - Platsen och besöksnäringen</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -18221,19 +18221,19 @@
       </c>
       <c r="I405" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>GBP3BC</t>
+          <t>GNA3B7</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -18243,18 +18243,18 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Nationalekonomi</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Fotografiskt bildskapande B</t>
+          <t>Mikroekonomi, introduktion</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -18264,19 +18264,19 @@
       </c>
       <c r="I406" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B7</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>GPG3BD</t>
+          <t>GBP3BB</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -18292,12 +18292,12 @@
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Introduktion till läraryrket</t>
+          <t>Fotografiskt bildskapande A</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -18307,19 +18307,19 @@
       </c>
       <c r="I407" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BB</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>GFI3BU</t>
+          <t>GBP3BC</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -18329,18 +18329,18 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="E408" t="inlineStr"/>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Introduktion till existentialismen</t>
+          <t>Fotografiskt bildskapande B</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -18350,19 +18350,19 @@
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BC</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>ABQ2AM</t>
+          <t>GPG3BD</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -18372,18 +18372,18 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Kreativ kodning</t>
+          <t>Introduktion till läraryrket</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -18393,19 +18393,19 @@
       </c>
       <c r="I409" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>GPG3CN</t>
+          <t>GFI3BU</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -18415,18 +18415,18 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
+          <t>Introduktion till existentialismen</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -18436,19 +18436,19 @@
       </c>
       <c r="I410" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>GHI3CP</t>
+          <t>ABQ2AM</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -18458,18 +18458,18 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel – inriktning historiedidaktik</t>
+          <t>Kreativ kodning</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -18479,19 +18479,19 @@
       </c>
       <c r="I411" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>GRK3CQ</t>
+          <t>GPG3CN</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -18501,18 +18501,18 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="E412" t="inlineStr"/>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
+          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -18522,19 +18522,19 @@
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>GMN3E2</t>
+          <t>GHI3CP</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -18544,18 +18544,18 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Dramaturgi, manusskrivande och medieproduktionens villkor</t>
+          <t>Undervisning och lärande genom rollspel – inriktning historiedidaktik</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -18565,19 +18565,19 @@
       </c>
       <c r="I413" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>GMN3EZ</t>
+          <t>GRK3CQ</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -18587,18 +18587,18 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Kandidatexamensarbete i Medieproduktion</t>
+          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -18608,14 +18608,14 @@
       </c>
       <c r="I414" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>GMN3EX</t>
+          <t>GMN3E2</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -18630,7 +18630,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Alternativa gestaltningsformer</t>
+          <t>Dramaturgi, manusskrivande och medieproduktionens villkor</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -18651,14 +18651,14 @@
       </c>
       <c r="I415" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E2</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>GMN3EY</t>
+          <t>GMN3EZ</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -18673,7 +18673,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E416" t="inlineStr"/>
@@ -18684,7 +18684,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Vetenskapsteori och metod i Medieproduktion</t>
+          <t>Kandidatexamensarbete i Medieproduktion</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -18694,14 +18694,14 @@
       </c>
       <c r="I416" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>GMN3F2</t>
+          <t>GMN3EX</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Exponeringsprojekt inom Medieproduktion</t>
+          <t>Alternativa gestaltningsformer</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -18737,19 +18737,19 @@
       </c>
       <c r="I417" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>GBQ3FG</t>
+          <t>GMN3EY</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -18759,18 +18759,18 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Kreativt skrivande</t>
+          <t>Vetenskapsteori och metod i Medieproduktion</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -18780,19 +18780,19 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EY</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>APG2BF</t>
+          <t>GMN3F2</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -18802,18 +18802,18 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Att främja en professionsdriven verksamhetsutveckling i förskola, skola och fritidshem</t>
+          <t>Exponeringsprojekt inom Medieproduktion</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -18823,19 +18823,19 @@
       </c>
       <c r="I419" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>APG2BK</t>
+          <t>GBQ3FG</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -18845,18 +18845,18 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 3 - VAL</t>
+          <t>Kreativt skrivande</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -18866,14 +18866,14 @@
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>APG2BF</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -18888,7 +18888,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Introduktion till studier i program - VAL</t>
+          <t>Att främja en professionsdriven verksamhetsutveckling i förskola, skola och fritidshem</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -18909,14 +18909,14 @@
       </c>
       <c r="I421" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>GPG3FS</t>
+          <t>APG2BK</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 1 - VAL</t>
+          <t>Verksamhetsförlagd utbildning 3 - VAL</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -18952,14 +18952,14 @@
       </c>
       <c r="I422" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>GPG3FT</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 2 - VAL</t>
+          <t>Introduktion till studier i program - VAL</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -18995,19 +18995,19 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>GMN3F3</t>
+          <t>GPG3FS</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -19017,18 +19017,18 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning inom medieproduktion</t>
+          <t>Verksamhetsförlagd utbildning 1 - VAL</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -19038,14 +19038,14 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E425" t="inlineStr"/>
@@ -19071,22 +19071,108 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
+          <t>Verksamhetsförlagd utbildning 2 - VAL</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>GMN3F3</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>MPR</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>IKS</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Medieproduktion</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Verksamhetsförlagd utbildning inom medieproduktion</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>APG2CC</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>IKS</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Pedagogiskt arbete</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
           <t>Mentorsutbildning för en kvalitativ introduktionsperiod</t>
         </is>
       </c>
-      <c r="H425" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I425" s="2" t="inlineStr">
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I425"/>
+  <autoFilter ref="A1:I427"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -19936,6 +20022,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I424" r:id="rId846"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A425" r:id="rId847"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I425" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A426" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I426" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A427" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I427" r:id="rId852"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$453</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$446</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I453"/>
+  <dimension ref="A1:I446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11307,12 +11307,12 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>ASK22M</t>
+          <t>GAB2AJ</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -11322,22 +11322,18 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Statsvetenskap</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i statsvetenskap</t>
+          <t>Att vara ledare</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -11347,19 +11343,19 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2AJ</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>GAB2AJ</t>
+          <t>GBQ2AY</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -11369,18 +11365,18 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2019-08-29</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Att vara ledare</t>
+          <t>Digital efterbearbetning av ljud och bild</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -11390,14 +11386,14 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2AY</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>GBQ2AY</t>
+          <t>GBQ2AZ</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -11423,7 +11419,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Digital efterbearbetning av ljud och bild</t>
+          <t>Ljussättning och färgkorrigering inom filmdesign</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -11433,19 +11429,19 @@
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2AY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2AZ</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>GBQ2AZ</t>
+          <t>GFÖ2B9</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -11461,12 +11457,12 @@
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Ljussättning och färgkorrigering inom filmdesign</t>
+          <t>Ledarskap och organisationsbeteende</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -11476,19 +11472,19 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2AZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ2B9</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>GFÖ2B9</t>
+          <t>FPA2227</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -11498,18 +11494,18 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2019-09-23</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Ledarskap och organisationsbeteende</t>
+          <t>Lärares ledarskap - villkor och praktik</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -11519,19 +11515,19 @@
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ2B9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>FPA2227</t>
+          <t>GLP2BQ</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -11541,18 +11537,18 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2019-09-23</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Lärares ledarskap - villkor och praktik</t>
+          <t>Medieproduktion som projektarbete</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -11562,19 +11558,19 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2BQ</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>GLP2BQ</t>
+          <t>FPA2226</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -11584,18 +11580,18 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2019-10-23</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Medieproduktion som projektarbete</t>
+          <t>Läsinlärning och läsutveckling i teori och praktik</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -11605,19 +11601,19 @@
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>FPA2226</t>
+          <t>GEU2CA</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -11627,18 +11623,18 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2019-10-23</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Läsinlärning och läsutveckling i teori och praktik</t>
+          <t>Det entreprenöriella företagets förutsättningar</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -11648,14 +11644,14 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CA</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>GEU2CA</t>
+          <t>GEU2CB</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -11681,7 +11677,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Det entreprenöriella företagets förutsättningar</t>
+          <t>Ledarskap och grupprocesser</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -11691,19 +11687,19 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CB</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>GEU2CB</t>
+          <t>GRV2CE</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -11719,12 +11715,12 @@
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Rättsvetenskap</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Ledarskap och grupprocesser</t>
+          <t>Småföretagens regelverk</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -11734,19 +11730,19 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>GRV2CE</t>
+          <t>GAB2CC</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -11756,18 +11752,18 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2019-11-28</t>
+          <t>2019-12-02</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rättsvetenskap</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Småföretagens regelverk</t>
+          <t>Ny som ledare</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -11777,19 +11773,19 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2CC</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>GAB2CC</t>
+          <t>FPA0003</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -11799,18 +11795,22 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2019-12-02</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr"/>
+          <t>2018-03-28</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>2019-12-18</t>
+        </is>
+      </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Ny som ledare</t>
+          <t>Akademiskt skrivande och talande  på engelska</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -11820,19 +11820,19 @@
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0003</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>FPA0003</t>
+          <t>GHI2CK</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -11842,22 +11842,18 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2018-03-28</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>2019-12-18</t>
-        </is>
-      </c>
+          <t>2020-01-30</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Akademiskt skrivande och talande  på engelska</t>
+          <t>Introduktion till svensk kultur och samhälle</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -11867,14 +11863,14 @@
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CK</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>GHI2CK</t>
+          <t>GHI2CN</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -11900,7 +11896,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Introduktion till svensk kultur och samhälle</t>
+          <t>Historia I</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -11910,14 +11906,14 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CN</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>GHI2CN</t>
+          <t>GHI2CP</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -11943,7 +11939,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Historia I</t>
+          <t>Historia I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -11953,14 +11949,14 @@
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CP</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>GHI2CP</t>
+          <t>GHI2CQ</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -11986,7 +11982,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Historia I med didaktisk inriktning</t>
+          <t>Historia II</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -11996,14 +11992,14 @@
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CQ</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>GHI2CQ</t>
+          <t>GHI2CR</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -12029,7 +12025,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Historia II</t>
+          <t>Historia II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -12039,19 +12035,19 @@
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CR</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>GHI2CR</t>
+          <t>GLP2CX</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -12061,18 +12057,18 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2020-01-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Historia II med didaktisk inriktning</t>
+          <t>Musikskapande</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -12082,19 +12078,19 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2CX</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>GLP2CX</t>
+          <t>GKG2CS</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -12104,18 +12100,18 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2020-01-31</t>
+          <t>2020-02-06</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Kulturgeografi</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Musikskapande</t>
+          <t>Marknadsanalyser med hjälp av GIS</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -12125,19 +12121,19 @@
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2CX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG2CS</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>GKG2CS</t>
+          <t>GBQ2EB</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -12147,18 +12143,18 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2020-02-06</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Kulturgeografi</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Marknadsanalyser med hjälp av GIS</t>
+          <t>Fakta, fiktion och flerkameraproduktion</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -12168,14 +12164,14 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG2CS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2EB</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>GBQ2EB</t>
+          <t>GBQ2EC</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -12201,7 +12197,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Fakta, fiktion och flerkameraproduktion</t>
+          <t>Fortsätt berätta med film om kulturarv och historia</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -12211,19 +12207,19 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2EB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2EC</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>GBQ2EC</t>
+          <t>GLP2FP</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -12239,12 +12235,12 @@
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Fortsätt berätta med film om kulturarv och historia</t>
+          <t>Ljudteori</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -12254,19 +12250,19 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2EC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FP</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>GLP2FP</t>
+          <t>GFÖ2FF</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -12276,18 +12272,18 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Ljudteori</t>
+          <t>Vetenskap och metod I</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -12297,19 +12293,19 @@
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ2FF</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>GFÖ2FF</t>
+          <t>GPA2FL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -12319,18 +12315,18 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-03-09</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Vetenskap och metod I</t>
+          <t>Samspel i organisationen - gruppen</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -12340,19 +12336,19 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ2FF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>GPA2FL</t>
+          <t>GLP2FH</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -12362,18 +12358,18 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2020-03-09</t>
+          <t>2020-03-10</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Samspel i organisationen - gruppen</t>
+          <t>Introduktion till medieproduktion</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -12383,19 +12379,19 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FH</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>GLP2FH</t>
+          <t>GHI2FU</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -12405,18 +12401,18 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2020-03-10</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Introduktion till medieproduktion</t>
+          <t>Introduktion till afrikastudier</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -12426,19 +12422,19 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2FU</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>GHI2FU</t>
+          <t>GLP2FZ</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -12448,18 +12444,18 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2020-03-12</t>
         </is>
       </c>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Introduktion till afrikastudier</t>
+          <t>Fördjupningskurs i Ljud- och musikproduktion med kandidatexamensarbete</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -12469,19 +12465,19 @@
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FZ</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>GLP2FZ</t>
+          <t>FPA222A</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -12491,18 +12487,18 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2020-03-12</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Fördjupningskurs i Ljud- och musikproduktion med kandidatexamensarbete</t>
+          <t>Vetenskapsteori och forskningsetik</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -12512,14 +12508,14 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222A</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>FPA222A</t>
+          <t>FPA2228</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -12534,7 +12530,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2020-06-09</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
@@ -12545,7 +12541,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Vetenskapsteori och forskningsetik</t>
+          <t>Introduktion till forskning i pedagogiskt arbete</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -12555,19 +12551,19 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2228</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>FPA2228</t>
+          <t>GBQ2HC</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -12577,18 +12573,18 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2020-06-09</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Introduktion till forskning i pedagogiskt arbete</t>
+          <t>Introduktion till produktion av rörlig bild för Manus för film och TV</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -12598,14 +12594,14 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2HC</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>GBQ2HC</t>
+          <t>GBQ2HD</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -12631,7 +12627,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Introduktion till produktion av rörlig bild för Manus för film och TV</t>
+          <t>Grunderna i filmproduktion för Manus för film och TV</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -12641,19 +12637,19 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2HC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2HD</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>GBQ2HD</t>
+          <t>FI1038</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -12663,18 +12659,22 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr"/>
+          <t>2010-10-19</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Grunderna i filmproduktion för Manus för film och TV</t>
+          <t>Samhällsvetenskapernas vetenskapsteori</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -12684,19 +12684,19 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2HD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1038</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>FI1038</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2010-10-19</t>
+          <t>2015-12-10</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -12716,12 +12716,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Samhällsvetenskapernas vetenskapsteori</t>
+          <t>Från idé till master</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -12731,19 +12731,19 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>FI1026</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -12753,22 +12753,22 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2015-12-10</t>
+          <t>2006-10-19</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Från idé till master</t>
+          <t>Filosofi: Moralfilosofi</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -12778,14 +12778,14 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1026</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>FI1026</t>
+          <t>FI1035</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2006-10-19</t>
+          <t>2010-02-16</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Filosofi: Moralfilosofi</t>
+          <t>Filosofi: 1900-talets filosofi</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -12825,14 +12825,14 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1035</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>FI1035</t>
+          <t>FI1036</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Filosofi: 1900-talets filosofi</t>
+          <t>Filosofi: Politisk filosofi</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -12872,14 +12872,14 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1036</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>FI1036</t>
+          <t>FI1037</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Filosofi: Politisk filosofi</t>
+          <t>Filosofi: Filosofiska klassiker</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -12919,14 +12919,14 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1037</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>FI1037</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2010-02-16</t>
+          <t>2011-05-30</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Filosofi: Filosofiska klassiker</t>
+          <t>Materialvetenskapens idéhistoria och vetenskapsteori</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -12966,19 +12966,19 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>HI1004</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2011-05-30</t>
+          <t>2007-01-09</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Materialvetenskapens idéhistoria och vetenskapsteori</t>
+          <t>Introduktion till svensk kultur och samhälle</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -13013,14 +13013,14 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1004</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>HI1004</t>
+          <t>HI1006</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2007-01-09</t>
+          <t>2009-05-28</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Introduktion till svensk kultur och samhälle</t>
+          <t>Globala rörelser för social rättvisa</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -13060,19 +13060,19 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1006</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>HI1006</t>
+          <t>FI1024</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -13082,22 +13082,22 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2009-05-28</t>
+          <t>2006-10-19</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2020-07-06</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Globala rörelser för social rättvisa</t>
+          <t>Filosofi: Två teman inom filosofi</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -13107,14 +13107,14 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>FI1024</t>
+          <t>FI2003</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2006-10-19</t>
+          <t>2010-02-16</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Filosofi: Två teman inom filosofi</t>
+          <t>Filosofi: Filosofi III</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -13154,19 +13154,19 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>SK1062</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -13176,22 +13176,22 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2010-02-16</t>
+          <t>2015-04-09</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2020-07-06</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Statsvetenskap</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Filosofi: Filosofi III</t>
+          <t>Förvaltning i Sverige och EU</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -13201,19 +13201,19 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>SK1062</t>
+          <t>AHI263</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -13223,22 +13223,18 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2015-04-09</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Statsvetenskap</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Förvaltning i Sverige och EU</t>
+          <t>Afrikanska studier: Islam och islamiska samhällen i Afrika</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -13248,19 +13244,19 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI263</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>AHI263</t>
+          <t>GPA2K3</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -13270,18 +13266,18 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Islam och islamiska samhällen i Afrika</t>
+          <t>Marknadsföring för personalvetare</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -13291,19 +13287,19 @@
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI263</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>GPA2K3</t>
+          <t>GLP2JZ</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -13313,18 +13309,18 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-09-30</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Marknadsföring för personalvetare</t>
+          <t>Audioteknologi 1</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -13334,14 +13330,14 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GLP2JZ</t>
+          <t>GLP2KH</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13356,7 +13352,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
@@ -13367,7 +13363,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Audioteknologi 1</t>
+          <t>Ljudskapande till rörliga bilder</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -13377,19 +13373,19 @@
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>GLP2KH</t>
+          <t>GRK2KL</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -13405,12 +13401,12 @@
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Ljudskapande till rörliga bilder</t>
+          <t>Mänskliga rättigheter: Examensarbete för kandidatexamen</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -13420,19 +13416,19 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2KH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>GRK2KL</t>
+          <t>GEU2KV</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -13442,18 +13438,18 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Mänskliga rättigheter: Examensarbete för kandidatexamen</t>
+          <t>Entreprenörskap i regional utveckling och tillväxt</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -13463,14 +13459,14 @@
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>GEU2KV</t>
+          <t>GEU2KW</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13496,7 +13492,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Entreprenörskap i regional utveckling och tillväxt</t>
+          <t>Entreprenörskapets teoretiska klassiker</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -13506,14 +13502,14 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KW</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GEU2KW</t>
+          <t>GEU2KX</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13539,7 +13535,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Entreprenörskapets teoretiska klassiker</t>
+          <t>Innovation A</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -13549,19 +13545,19 @@
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KX</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GEU2KX</t>
+          <t>GPA2KU</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -13577,12 +13573,12 @@
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Innovation A</t>
+          <t>Implementering av hållbar strategisk styrning</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -13592,19 +13588,19 @@
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>GPA2KU</t>
+          <t>APG26D</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -13620,12 +13616,12 @@
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Implementering av hållbar strategisk styrning</t>
+          <t>Didaktisk analys för fortsatt professionsutveckling</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -13635,19 +13631,19 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>APG26D</t>
+          <t>FPA222B</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -13657,7 +13653,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
@@ -13668,7 +13664,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Didaktisk analys för fortsatt professionsutveckling</t>
+          <t>Vetenskapliga metoder</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -13678,14 +13674,14 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222B</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>FPA222B</t>
+          <t>FPA0007</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13700,10 +13696,14 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2020-12-02</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr"/>
+          <t>2018-05-30</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>2020-12-16</t>
+        </is>
+      </c>
       <c r="F301" t="inlineStr">
         <is>
           <t>Pedagogiskt arbete</t>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Vetenskapliga metoder</t>
+          <t>Intellektuella utmaningar -  att designa och kommunicera ett forskningsprojekt</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -13721,19 +13721,19 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>FPA0007</t>
+          <t>GPA2LM</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -13743,22 +13743,18 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2018-05-30</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>2020-12-16</t>
-        </is>
-      </c>
+          <t>2021-01-28</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Intellektuella utmaningar -  att designa och kommunicera ett forskningsprojekt</t>
+          <t>Personal och arbetsliv - en introduktion</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -13768,14 +13764,14 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>GPA2LM</t>
+          <t>GPA2LN</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13801,7 +13797,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv - en introduktion</t>
+          <t>Ekonomi- och verksamhetsstyrning för personalvetare</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -13811,19 +13807,19 @@
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>GPA2LN</t>
+          <t>FPA222C</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -13833,18 +13829,18 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-02-02</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Ekonomi- och verksamhetsstyrning för personalvetare</t>
+          <t>Praktikutvecklande forskningsansatser för undervisning och lärande</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -13854,19 +13850,19 @@
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222C</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>FPA222C</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -13876,18 +13872,18 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Rättsvetenskap</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Praktikutvecklande forskningsansatser för undervisning och lärande</t>
+          <t>Småföretagens regelverk I</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -13897,19 +13893,19 @@
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>AHI26P</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -13919,18 +13915,18 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Rättsvetenskap</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Småföretagens regelverk I</t>
+          <t>Afrikanska studier: Islam och islamiska samhällen i Afrika</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -13940,19 +13936,19 @@
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI26P</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>AHI26P</t>
+          <t>GLP2MS</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -13968,12 +13964,12 @@
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Islam och islamiska samhällen i Afrika</t>
+          <t>Kommunikationsteorier</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -13983,19 +13979,19 @@
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI26P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MS</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>GLP2MS</t>
+          <t>GBQ2MT</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -14005,18 +14001,18 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Kommunikationsteorier</t>
+          <t>Dokumentärfilmproduktion</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -14026,19 +14022,19 @@
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2MT</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>GBQ2MT</t>
+          <t>GAB2P6</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -14048,18 +14044,18 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Dokumentärfilmproduktion</t>
+          <t>Professionell distanskommunikation</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -14069,19 +14065,19 @@
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2MT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2P6</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>GAB2P6</t>
+          <t>GNA2NT</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -14097,12 +14093,12 @@
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Nationalekonomi</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Professionell distanskommunikation</t>
+          <t>Finansiella marknader och penningpolitik</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -14112,19 +14108,19 @@
       </c>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2P6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>GNA2NT</t>
+          <t>GPA2P7</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -14140,12 +14136,12 @@
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Nationalekonomi</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Finansiella marknader och penningpolitik</t>
+          <t>Samhällsvetenskaplig metod och vetenskapsteori II</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -14155,19 +14151,19 @@
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>GPA2P7</t>
+          <t>GBQ2NH</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -14177,18 +14173,18 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Samhällsvetenskaplig metod och vetenskapsteori II</t>
+          <t>Projektplanering och användarperspektiv</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -14198,14 +14194,14 @@
       </c>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NH</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>GBQ2NH</t>
+          <t>GBQ2NM</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14231,7 +14227,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Projektplanering och användarperspektiv</t>
+          <t>Vetenskapsteori och metod i Bildproduktion</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -14241,14 +14237,14 @@
       </c>
       <c r="I313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NM</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GBQ2NM</t>
+          <t>GBQ2NP</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14274,7 +14270,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Vetenskapsteori och metod i Bildproduktion</t>
+          <t>Kandidatexamensarbete i Bildproduktion</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -14284,19 +14280,19 @@
       </c>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NP</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>GBQ2NP</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -14312,12 +14308,12 @@
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Kandidatexamensarbete i Bildproduktion</t>
+          <t>Kabbala och judisk mystik från antiken till modern tid</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -14327,19 +14323,19 @@
       </c>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>FPA222D</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -14349,18 +14345,18 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Kabbala och judisk mystik från antiken till modern tid</t>
+          <t>Språklig mångfald i utbildningssammanhang</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -14370,19 +14366,19 @@
       </c>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222D</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>FPA222D</t>
+          <t>GPG2N7</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -14392,10 +14388,14 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
           <t>2021-03-15</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
           <t>Pedagogiskt arbete</t>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Språklig mångfald i utbildningssammanhang</t>
+          <t>Skolväsendets historia</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -14413,19 +14413,19 @@
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>GPG2N7</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -14435,22 +14435,18 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>2021-03-15</t>
-        </is>
-      </c>
+          <t>2021-03-18</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Skolväsendets historia</t>
+          <t>Religionsvetenskap III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -14460,19 +14456,19 @@
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -14482,18 +14478,18 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Statsvetenskap</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Religionsvetenskap III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Examensarbete för högskoleexamen i statsvetenskap</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -14503,14 +14499,14 @@
       </c>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14536,7 +14532,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Examensarbete för högskoleexamen i statsvetenskap</t>
+          <t>Examensarbete för kandidatexamen i statsvetenskap</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -14546,19 +14542,19 @@
       </c>
       <c r="I320" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>FPA222E</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -14568,18 +14564,18 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-05-04</t>
         </is>
       </c>
       <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Statsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i statsvetenskap</t>
+          <t>Intellektuella utmaningar – att formulera och undersöka ett problem</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -14589,14 +14585,14 @@
       </c>
       <c r="I321" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>FPA222E</t>
+          <t>FPA222F</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14622,7 +14618,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Intellektuella utmaningar – att formulera och undersöka ett problem</t>
+          <t>Akademiskt skrivande och talande på engelska</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -14632,14 +14628,14 @@
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222F</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>FPA222F</t>
+          <t>FPA222G</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14665,7 +14661,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Akademiskt skrivande och talande på engelska</t>
+          <t>Forskningskommunikation för samhällsutveckling</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -14675,19 +14671,19 @@
       </c>
       <c r="I323" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>FPA222G</t>
+          <t>GBQ2QB</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -14697,18 +14693,18 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2021-05-04</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Forskningskommunikation för samhällsutveckling</t>
+          <t>Kvalificerat filmmanusprojekt</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -14718,19 +14714,19 @@
       </c>
       <c r="I324" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2QB</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>GBQ2QB</t>
+          <t>GLP2QC</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -14746,12 +14742,12 @@
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Kvalificerat filmmanusprojekt</t>
+          <t>Projektarbete inom medieproduktion, fördjupningskurs</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -14761,14 +14757,14 @@
       </c>
       <c r="I325" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2QB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QC</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>GLP2QC</t>
+          <t>GLP2QD</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14794,7 +14790,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Projektarbete inom medieproduktion, fördjupningskurs</t>
+          <t>Arbetsplatsförlagd utbildning i medieproduktion</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -14804,14 +14800,14 @@
       </c>
       <c r="I326" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QD</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>GLP2QD</t>
+          <t>GLP2QU</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14826,7 +14822,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E327" t="inlineStr"/>
@@ -14837,7 +14833,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Arbetsplatsförlagd utbildning i medieproduktion</t>
+          <t>Inspelning i studio</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -14847,14 +14843,14 @@
       </c>
       <c r="I327" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QU</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>GLP2QU</t>
+          <t>GLP2QX</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14869,7 +14865,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="E328" t="inlineStr"/>
@@ -14880,7 +14876,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Inspelning i studio</t>
+          <t>Möten med skilda musikgenrer</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -14890,19 +14886,19 @@
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>GLP2QX</t>
+          <t>GEU2QY</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -14912,18 +14908,18 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Möten med skilda musikgenrer</t>
+          <t>Ledarskap</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -14933,19 +14929,19 @@
       </c>
       <c r="I329" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2QY</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>GEU2QY</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -14955,18 +14951,18 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Ledarskap</t>
+          <t>Kompetensförsörjning - avveckling och förändring</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -14976,19 +14972,19 @@
       </c>
       <c r="I330" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2QY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -15004,12 +15000,12 @@
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Kompetensförsörjning - avveckling och förändring</t>
+          <t>Religionsvetenskap III: Uppsats</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -15019,14 +15015,14 @@
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -15052,7 +15048,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Religionsvetenskap III: Uppsats</t>
+          <t>Religionsvetenskap III: Examensarbete för kandidatexamen</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -15062,19 +15058,19 @@
       </c>
       <c r="I332" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>SO1019</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -15084,18 +15080,22 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
+          <t>2010-10-19</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Sociologi</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Religionsvetenskap III: Examensarbete för kandidatexamen</t>
+          <t>Introduktion till samhällsvetenskap</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -15105,19 +15105,19 @@
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>GNA2RY</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -15127,22 +15127,18 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2010-10-19</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
+          <t>2021-10-29</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Sociologi</t>
+          <t>Nationalekonomi</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Introduktion till samhällsvetenskap</t>
+          <t>Statistik för ekonomer</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -15152,19 +15148,19 @@
       </c>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2RY</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>GNA2RY</t>
+          <t>GAB2S5</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -15174,18 +15170,18 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Nationalekonomi</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Statistik för ekonomer</t>
+          <t>Arbetsmiljö</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -15195,19 +15191,19 @@
       </c>
       <c r="I335" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2RY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2S5</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>GAB2S5</t>
+          <t>GPE2SA</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -15217,18 +15213,18 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Pedagogik</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Arbetsmiljö</t>
+          <t>Utbildningssystemet i Sverige</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -15238,19 +15234,19 @@
       </c>
       <c r="I336" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2S5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE2SA</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>GPE2SA</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -15266,12 +15262,12 @@
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Pedagogik</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Utbildningssystemet i Sverige</t>
+          <t>Samhällsorienterande ämnen, årskurs 4-6</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -15281,19 +15277,19 @@
       </c>
       <c r="I337" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE2SA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GAB2TR</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -15303,18 +15299,18 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2021-12-03</t>
+          <t>2021-12-07</t>
         </is>
       </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Samhällsorienterande ämnen, årskurs 4-6</t>
+          <t>Förståelse och förhållningssätt för främjande av utvecklingsprocesser</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -15324,19 +15320,19 @@
       </c>
       <c r="I338" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2TR</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>GAB2TR</t>
+          <t>GPG2SG</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -15346,18 +15342,18 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2021-12-07</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Förståelse och förhållningssätt för främjande av utvecklingsprocesser</t>
+          <t>Omsorg, relationer och etik i förskolläraryrket</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -15367,14 +15363,14 @@
       </c>
       <c r="I339" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2TR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>GPG2SG</t>
+          <t>GPG2SH</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -15400,7 +15396,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Omsorg, relationer och etik i förskolläraryrket</t>
+          <t>Lek i förskolan (varav 7,5 hp VFU)</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -15410,14 +15406,14 @@
       </c>
       <c r="I340" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>GPG2SH</t>
+          <t>GPG2TT</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -15432,7 +15428,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
@@ -15443,7 +15439,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Lek i förskolan (varav 7,5 hp VFU)</t>
+          <t>Omsorg, relationer och etik i förskolläraryrket</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -15453,19 +15449,19 @@
       </c>
       <c r="I341" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>GPG2TT</t>
+          <t>GBQ2U3</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -15475,18 +15471,18 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2021-12-22</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Omsorg, relationer och etik i förskolläraryrket</t>
+          <t>Människan och den rörliga bilden</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -15496,14 +15492,14 @@
       </c>
       <c r="I342" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U3</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U3</t>
+          <t>GBQ2U4</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -15529,7 +15525,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Människan och den rörliga bilden</t>
+          <t>Informationsfilmsproduktion</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -15539,14 +15535,14 @@
       </c>
       <c r="I343" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U4</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U4</t>
+          <t>GBQ2U5</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -15572,7 +15568,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Informationsfilmsproduktion</t>
+          <t>Kvalificerad filmdesign i transmedia</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -15582,14 +15578,14 @@
       </c>
       <c r="I344" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U5</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U5</t>
+          <t>GBQ2U6</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -15615,7 +15611,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Kvalificerad filmdesign i transmedia</t>
+          <t>Projektplanering och användarperspektiv</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -15625,14 +15621,14 @@
       </c>
       <c r="I345" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U6</t>
+          <t>GBQ2U7</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -15658,7 +15654,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Projektplanering och användarperspektiv</t>
+          <t>Tillämpad filmdesign 1</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -15668,14 +15664,14 @@
       </c>
       <c r="I346" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U7</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U7</t>
+          <t>GBQ2U8</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -15701,7 +15697,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Tillämpad filmdesign 1</t>
+          <t>Den korta filmens berättarstruktur</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -15711,19 +15707,19 @@
       </c>
       <c r="I347" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U8</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U8</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -15739,12 +15735,12 @@
       <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Den korta filmens berättarstruktur</t>
+          <t>Kvinnor och gudinnor på gränsen till den äldsta förhistorien</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -15754,19 +15750,19 @@
       </c>
       <c r="I348" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>GBQ2UB</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -15776,18 +15772,18 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
+          <t>2022-02-07</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Kvinnor och gudinnor på gränsen till den äldsta förhistorien</t>
+          <t>Introduktion till produktion av rörlig bild</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -15797,19 +15793,19 @@
       </c>
       <c r="I349" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>GBQ2UB</t>
+          <t>GLP2UG</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -15819,18 +15815,18 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Introduktion till produktion av rörlig bild</t>
+          <t>Ljudskapande till rörliga bilder</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -15840,19 +15836,19 @@
       </c>
       <c r="I350" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2UG</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>GLP2UG</t>
+          <t>GBQ2UN</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -15862,18 +15858,18 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Ljudskapande till rörliga bilder</t>
+          <t>Filmanalys och gestaltning</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -15883,19 +15879,19 @@
       </c>
       <c r="I351" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2UG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UN</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>GBQ2UN</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -15911,12 +15907,12 @@
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Filmanalys och gestaltning</t>
+          <t>Naturbaserad turism</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -15926,19 +15922,19 @@
       </c>
       <c r="I352" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -15948,18 +15944,18 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Naturbaserad turism</t>
+          <t>Rektors ledning och organisering för utveckling av barns och elevers lärandemiljö</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -15969,14 +15965,14 @@
       </c>
       <c r="I353" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>APG27U</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -15991,7 +15987,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
@@ -16002,7 +15998,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Rektors ledning och organisering för utveckling av barns och elevers lärandemiljö</t>
+          <t>Utvärdering och verksamhetsutveckling i förskola och förskoleklass (varav 7,5 hp VFU)</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -16012,19 +16008,19 @@
       </c>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>APG27U</t>
+          <t>GLP2VS</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -16034,18 +16030,18 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-03-09</t>
         </is>
       </c>
       <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Utvärdering och verksamhetsutveckling i förskola och förskoleklass (varav 7,5 hp VFU)</t>
+          <t>Arbetsplatsförlagd utbildning i medieproduktion</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -16055,14 +16051,14 @@
       </c>
       <c r="I355" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VS</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>GLP2VS</t>
+          <t>GLP2VT</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -16077,7 +16073,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2022-03-09</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
@@ -16088,7 +16084,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Arbetsplatsförlagd utbildning i medieproduktion</t>
+          <t>Produktionsprocesser inom musikproduktion</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -16098,19 +16094,19 @@
       </c>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>GLP2VT</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -16120,18 +16116,18 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
+          <t>2022-03-15</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Produktionsprocesser inom musikproduktion</t>
+          <t>Professionellt lärarskap och skolutveckling (varav 10 hp VFU)</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -16141,19 +16137,19 @@
       </c>
       <c r="I357" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GLP2WB</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -16163,18 +16159,18 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2022-03-15</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Professionellt lärarskap och skolutveckling (varav 10 hp VFU)</t>
+          <t>Liveljud och liveinspelning</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -16184,14 +16180,14 @@
       </c>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WB</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>GLP2WB</t>
+          <t>GLP2WC</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -16217,7 +16213,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Liveljud och liveinspelning</t>
+          <t>Projektarbete inom medieproduktion, fördjupningskurs</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -16227,19 +16223,19 @@
       </c>
       <c r="I359" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WC</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>GLP2WC</t>
+          <t>GBQ2WG</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -16249,18 +16245,18 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Projektarbete inom medieproduktion, fördjupningskurs</t>
+          <t>Audiovisuell information och etik</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -16270,14 +16266,14 @@
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2WC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WG</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WG</t>
+          <t>GBQ2WH</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -16303,7 +16299,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Audiovisuell information och etik</t>
+          <t>Tillämpad filmdesign 2</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -16313,14 +16309,14 @@
       </c>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WH</t>
+          <t>GBQ2WJ</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -16346,7 +16342,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Tillämpad filmdesign 2</t>
+          <t>Reklamfilmsproduktion</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -16356,14 +16352,14 @@
       </c>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WJ</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WJ</t>
+          <t>GBQ2WK</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -16389,7 +16385,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Reklamfilmsproduktion</t>
+          <t>Ljussättning och färgkorrigering inom filmdesign</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -16399,19 +16395,19 @@
       </c>
       <c r="I363" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WK</t>
+          <t>GFÖ2WN</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -16421,18 +16417,18 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Ljussättning och färgkorrigering inom filmdesign</t>
+          <t>Redovisning B</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -16442,19 +16438,19 @@
       </c>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ2WN</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>GFÖ2WN</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -16470,12 +16466,12 @@
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Redovisning B</t>
+          <t>Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -16485,19 +16481,19 @@
       </c>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ2WN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>GBQ2XC</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -16507,18 +16503,18 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)</t>
+          <t>Manus för TV och film 3. Dialog i audiovisuella medier</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -16528,14 +16524,14 @@
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2XC</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>GBQ2XC</t>
+          <t>GBQ2XD</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -16561,7 +16557,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Manus för TV och film 3. Dialog i audiovisuella medier</t>
+          <t>Ljudinspelning och ljudläggning inom filmdesign</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -16571,19 +16567,19 @@
       </c>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2XC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2XD</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>GBQ2XD</t>
+          <t>FPA222J</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -16593,18 +16589,18 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Ljudinspelning och ljudläggning inom filmdesign</t>
+          <t>Grundläggande statistik för utbildningsvetenskaplig forskning</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -16614,14 +16610,14 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2XD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>FPA222J</t>
+          <t>FPA222N</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -16636,7 +16632,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
@@ -16647,7 +16643,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Grundläggande statistik för utbildningsvetenskaplig forskning</t>
+          <t>Vetenskapliga metoder för forskning i pedagogiskt arbete</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -16657,19 +16653,19 @@
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>FPA222N</t>
+          <t>GRK323</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -16679,18 +16675,18 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Vetenskapliga metoder för forskning i pedagogiskt arbete</t>
+          <t>Jerusalem som religiöst, historiskt och politiskt konfliktfylld plats. Berättelser ur ämnesdidaktiska perspektiv</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -16700,19 +16696,19 @@
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>GHI32G</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -16722,18 +16718,18 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Statsvetenskap</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Samhällsvetenskapliga metoder III - inriktning statsvetenskap</t>
+          <t>Historia II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -16743,19 +16739,19 @@
       </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI32G</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>GPA32D</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -16765,18 +16761,18 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning för lärare (KPU)</t>
+          <t>Individuella lärprocesser och kompetensutveckling</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -16786,19 +16782,19 @@
       </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>GLP33C</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -16808,18 +16804,18 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2023-02-24</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning för lärare (YRK)</t>
+          <t>Audiovisuell produktion för pedagogisk verksamhet</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -16829,19 +16825,19 @@
       </c>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP33C</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>GRK323</t>
+          <t>GPG33E</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -16851,18 +16847,18 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Jerusalem som religiöst, historiskt och politiskt konfliktfylld plats. Berättelser ur ämnesdidaktiska perspektiv</t>
+          <t>Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -16872,19 +16868,19 @@
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>GHI32G</t>
+          <t>AS3001</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -16894,18 +16890,22 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
-        </is>
-      </c>
-      <c r="E375" t="inlineStr"/>
+          <t>2014-12-10</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Afrikanska studier</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Historia II med didaktisk inriktning</t>
+          <t>Afrikanska studier: Utbildning och förändring i afrikanska samhällen</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -16915,19 +16915,19 @@
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI32G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>GPA32D</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -16937,18 +16937,22 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
-        </is>
-      </c>
-      <c r="E376" t="inlineStr"/>
+          <t>2014-12-10</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Afrikanska studier</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Individuella lärprocesser och kompetensutveckling</t>
+          <t>Afrikanska studier: Afrikanska samhällen i förändring</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -16958,19 +16962,19 @@
       </c>
       <c r="I376" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>GLP33C</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -16980,18 +16984,22 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="E377" t="inlineStr"/>
+          <t>2014-12-10</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Afrikanska studier</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Audiovisuell produktion för pedagogisk verksamhet</t>
+          <t>Afrikanska studier: Religion och politik i afrikanska samhällen</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -17001,19 +17009,19 @@
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP33C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>GPG33E</t>
+          <t>AS3004</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -17023,18 +17031,22 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr"/>
+          <t>2015-06-17</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Afrikanska studier</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL</t>
+          <t>Afrikanska studier: Forskningsprojektets planering</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -17044,19 +17056,19 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -17066,22 +17078,18 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
+          <t>2023-03-13</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Afrikanska studier</t>
+          <t>Sociologi</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Utbildning och förändring i afrikanska samhällen</t>
+          <t>Sociologi III</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -17091,19 +17099,19 @@
       </c>
       <c r="I379" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>GAB358</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -17113,22 +17121,18 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Afrikanska studier</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Afrikanska samhällen i förändring</t>
+          <t>Styrsystem och utveckling i socialtjänst/omsorg</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -17138,19 +17142,19 @@
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB358</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>GPA353</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -17160,22 +17164,18 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Afrikanska studier</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Religion och politik i afrikanska samhällen</t>
+          <t>Ledarskap</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -17185,19 +17185,19 @@
       </c>
       <c r="I381" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA353</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>AS3004</t>
+          <t>GPA354</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -17207,22 +17207,18 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2015-06-17</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Afrikanska studier</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Forskningsprojektets planering</t>
+          <t>Arbetsrätt, avtal och förhandling</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -17232,19 +17228,19 @@
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>GPA357</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -17254,18 +17250,18 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Sociologi</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Sociologi III</t>
+          <t>Praktik för personalvetare</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -17275,19 +17271,19 @@
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA357</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>GAB358</t>
+          <t>GLP359</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -17297,18 +17293,18 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Styrsystem och utveckling i socialtjänst/omsorg</t>
+          <t>Dansmusikhistoria och klubbkultur 1: DJ-kulturens utveckling 1970-2000</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -17318,19 +17314,19 @@
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB358</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>GPA353</t>
+          <t>GFÖ35J</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -17340,18 +17336,18 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Ledarskap</t>
+          <t>Turismmarknadsföring</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -17361,19 +17357,19 @@
       </c>
       <c r="I385" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA353</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ35J</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>GPA354</t>
+          <t>GBQ35K</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -17383,18 +17379,18 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Arbetsrätt, avtal och förhandling</t>
+          <t>Berätta med film om kulturarv och historia</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -17404,19 +17400,19 @@
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ35K</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>GPA357</t>
+          <t>GEU35L</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -17426,18 +17422,18 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Praktik för personalvetare</t>
+          <t>Projektledning I</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -17447,19 +17443,19 @@
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA357</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35L</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>GLP359</t>
+          <t>GEU35M</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -17469,18 +17465,18 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Dansmusikhistoria och klubbkultur 1: DJ-kulturens utveckling 1970-2000</t>
+          <t>Entreprenörskap - villkor och särart</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -17490,19 +17486,19 @@
       </c>
       <c r="I388" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35M</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>GFÖ35J</t>
+          <t>GEU35N</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -17512,18 +17508,18 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Turismmarknadsföring</t>
+          <t>Projektledning II</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -17533,14 +17529,14 @@
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ35J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35N</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>GBQ35K</t>
+          <t>GBQ36D</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -17555,7 +17551,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -17566,7 +17562,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Berätta med film om kulturarv och historia</t>
+          <t>Kvalificerad filmproduktion</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -17576,19 +17572,19 @@
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ35K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36D</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>GEU35L</t>
+          <t>ARK29H</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -17598,18 +17594,18 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Projektledning I</t>
+          <t>Religionsvetenskaplig litteraturkurs</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -17619,19 +17615,19 @@
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>GEU35M</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -17641,18 +17637,18 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Entreprenörskap - villkor och särart</t>
+          <t>Didaktik och läroplansteori - KPU</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -17662,19 +17658,19 @@
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>GEU35N</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -17684,18 +17680,18 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Projektledning II</t>
+          <t>Didaktik och läroplansteori</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -17705,14 +17701,14 @@
       </c>
       <c r="I393" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>GBQ36D</t>
+          <t>GBQ36K</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -17727,7 +17723,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
@@ -17738,7 +17734,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Kvalificerad filmproduktion</t>
+          <t>Flerkameraproduktion, fördjupning</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -17748,19 +17744,19 @@
       </c>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>ARK29H</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -17770,18 +17766,18 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Religionsvetenskaplig litteraturkurs</t>
+          <t>Historievetenskaplig litteraturkurs</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -17791,19 +17787,19 @@
       </c>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>AHI29R</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -17813,18 +17809,18 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Didaktik och läroplansteori - KPU</t>
+          <t>Historievetenskapens teori och metod</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -17834,19 +17830,19 @@
       </c>
       <c r="I396" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GHI37M</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -17856,18 +17852,18 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Didaktik och läroplansteori</t>
+          <t>De nationella minoriteternas samhällshistoria</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -17877,19 +17873,19 @@
       </c>
       <c r="I397" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI37M</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>GBQ36K</t>
+          <t>GFI37Z</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -17899,18 +17895,18 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-12-07</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Flerkameraproduktion, fördjupning</t>
+          <t>Gud och bevisen: filosofiska argument för och mot Guds existens</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -17920,14 +17916,14 @@
       </c>
       <c r="I398" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>GHI38Q</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -17942,7 +17938,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
@@ -17953,7 +17949,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Historievetenskaplig litteraturkurs</t>
+          <t>Global miljöhistoria</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -17963,19 +17959,19 @@
       </c>
       <c r="I399" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI38Q</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>AHI29R</t>
+          <t>GBQ38X</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -17985,18 +17981,18 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Historievetenskapens teori och metod</t>
+          <t>Fortsätt berätta med film om kulturarv och historia</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -18006,19 +18002,19 @@
       </c>
       <c r="I400" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>GHI37M</t>
+          <t>GEU38C</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -18028,18 +18024,18 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>De nationella minoriteternas samhällshistoria</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -18049,19 +18045,19 @@
       </c>
       <c r="I401" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI37M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU38C</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>GFI37Z</t>
+          <t>APG2AA</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -18071,18 +18067,18 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2023-12-07</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Gud och bevisen: filosofiska argument för och mot Guds existens</t>
+          <t>Lärarskicklighet - utveckling av lärarskicklighet i förskola och skola utifrån forskning</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -18092,19 +18088,19 @@
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>GHI38Q</t>
+          <t>GFÖ39A</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -18114,18 +18110,18 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Global miljöhistoria</t>
+          <t>Sport Management III</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -18135,14 +18131,14 @@
       </c>
       <c r="I403" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI38Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ39A</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>GBQ38X</t>
+          <t>GBQ3A5</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -18157,7 +18153,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="E404" t="inlineStr"/>
@@ -18168,7 +18164,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Fortsätt berätta med film om kulturarv och historia</t>
+          <t>Grunderna i filmproduktion</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -18178,19 +18174,19 @@
       </c>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A5</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>GEU38C</t>
+          <t>GBQ3A6</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -18200,18 +18196,18 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>Konceptutveckling för korta filmer</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -18221,19 +18217,19 @@
       </c>
       <c r="I405" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU38C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>APG2AA</t>
+          <t>GBQ3A7</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -18243,18 +18239,18 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Lärarskicklighet - utveckling av lärarskicklighet i förskola och skola utifrån forskning</t>
+          <t>Star Wars: Film, myter och världar</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -18264,19 +18260,19 @@
       </c>
       <c r="I406" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>GFÖ39A</t>
+          <t>GBQ3A8</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -18286,18 +18282,18 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Sport Management III</t>
+          <t>Kreativt skrivande</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -18307,14 +18303,14 @@
       </c>
       <c r="I407" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ39A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A8</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A5</t>
+          <t>GBQ3A9</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -18340,7 +18336,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Grunderna i filmproduktion</t>
+          <t>Introduktion till att skriva filmadaption</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -18350,14 +18346,14 @@
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A9</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A6</t>
+          <t>GBQ3AA</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -18383,7 +18379,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Konceptutveckling för korta filmer</t>
+          <t>Filmhistoria: En introduktion</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -18393,19 +18389,19 @@
       </c>
       <c r="I409" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A7</t>
+          <t>GTR3A4</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -18421,12 +18417,12 @@
       <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Star Wars: Film, myter och världar</t>
+          <t>Kvantitativ metod</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -18436,19 +18432,19 @@
       </c>
       <c r="I410" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A8</t>
+          <t>APG2AB</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -18458,18 +18454,18 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Kreativt skrivande</t>
+          <t>Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -18479,19 +18475,19 @@
       </c>
       <c r="I411" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AB</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A9</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -18501,18 +18497,18 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="E412" t="inlineStr"/>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Introduktion till att skriva filmadaption</t>
+          <t>Rektors pedagogiska ledarskap med fokus på förskolans utbildningsuppdrag</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -18522,19 +18518,19 @@
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AA</t>
+          <t>GPG3AF</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -18544,18 +18540,18 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Filmhistoria: En introduktion</t>
+          <t>Specialpedagogik och ett läraruppdrag i förändring för ämneslärare årskurs 7–9 - AIL</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -18565,19 +18561,19 @@
       </c>
       <c r="I413" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>GTR3A4</t>
+          <t>GPG3AG</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -18587,18 +18583,18 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Kvantitativ metod</t>
+          <t>Verksamhetsförlagd utbildning 2 för ämneslärare årskurs 7–9 - AIL</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -18608,19 +18604,19 @@
       </c>
       <c r="I414" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>APG2AB</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -18630,18 +18626,18 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL</t>
+          <t>Hårdrock och metal: musikproduktion, kultur och kreativa konventioner</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -18651,19 +18647,19 @@
       </c>
       <c r="I415" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>GAB3AK</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -18673,18 +18669,18 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Rektors pedagogiska ledarskap med fokus på förskolans utbildningsuppdrag</t>
+          <t>Kommunal styrning och förändringsarbete</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -18694,19 +18690,19 @@
       </c>
       <c r="I416" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AK</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>GPG3AD</t>
+          <t>GAB3AL</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -18716,18 +18712,18 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 1 för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Ledarskapets juridik</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -18737,19 +18733,19 @@
       </c>
       <c r="I417" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AL</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>GPG3AF</t>
+          <t>GPE3AJ</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -18759,18 +18755,18 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Pedagogik</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Specialpedagogik och ett läraruppdrag i förändring för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Att leda kollegiala lärprocesser i förskola och skola</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -18780,19 +18776,19 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>GPG3AG</t>
+          <t>GLP3AR</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -18802,18 +18798,18 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 2 för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Ljud- och musikproduktion med Pro Tools</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -18823,19 +18819,19 @@
       </c>
       <c r="I419" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>GBQ3AV</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -18845,18 +18841,18 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Hårdrock och metal: musikproduktion, kultur och kreativa konventioner</t>
+          <t>Content för sociala medier</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -18866,19 +18862,19 @@
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>GAB3AK</t>
+          <t>GBQ3AW</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -18888,18 +18884,18 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Kommunal styrning och förändringsarbete</t>
+          <t>Explainers med rörlig grafik</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -18909,19 +18905,19 @@
       </c>
       <c r="I421" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>GAB3AL</t>
+          <t>GTR3B6</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -18931,18 +18927,18 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Ledarskapets juridik</t>
+          <t>Sälenfjällen - Platsen och besöksnäringen</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -18952,19 +18948,19 @@
       </c>
       <c r="I422" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>GPE3AJ</t>
+          <t>GNA3B7</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -18974,18 +18970,18 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Pedagogik</t>
+          <t>Nationalekonomi</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Att leda kollegiala lärprocesser i förskola och skola</t>
+          <t>Mikroekonomi, introduktion</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -18995,19 +18991,19 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B7</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>GLP3AR</t>
+          <t>GRV3BF</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -19017,18 +19013,18 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Rättsvetenskap</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion med Pro Tools</t>
+          <t>IT-rätt</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -19038,19 +19034,19 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AV</t>
+          <t>GBP3BB</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -19060,18 +19056,18 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="E425" t="inlineStr"/>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Content för sociala medier</t>
+          <t>Fotografiskt bildskapande A</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -19081,19 +19077,19 @@
       </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BB</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AW</t>
+          <t>GBP3BC</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -19103,18 +19099,18 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Explainers med rörlig grafik</t>
+          <t>Fotografiskt bildskapande B</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -19124,19 +19120,19 @@
       </c>
       <c r="I426" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BC</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>GTR3B6</t>
+          <t>GPG3BD</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -19146,18 +19142,18 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Sälenfjällen - Platsen och besöksnäringen</t>
+          <t>Introduktion till läraryrket</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -19167,19 +19163,19 @@
       </c>
       <c r="I427" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>GNA3B7</t>
+          <t>GFI3BU</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -19189,18 +19185,18 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Nationalekonomi</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Mikroekonomi, introduktion</t>
+          <t>Introduktion till existentialismen</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -19210,19 +19206,19 @@
       </c>
       <c r="I428" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>ABQ2AM</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -19232,18 +19228,18 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr">
         <is>
-          <t>Rättsvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>IT-rätt</t>
+          <t>Kreativ kodning</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -19253,19 +19249,19 @@
       </c>
       <c r="I429" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>GBP3BB</t>
+          <t>GPG3CN</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -19275,18 +19271,18 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Fotografiskt bildskapande A</t>
+          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -19296,19 +19292,19 @@
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>GBP3BC</t>
+          <t>GHI3CP</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -19318,18 +19314,18 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="E431" t="inlineStr"/>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Fotografiskt bildskapande B</t>
+          <t>Undervisning och lärande genom rollspel – inriktning historiedidaktik</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -19339,19 +19335,19 @@
       </c>
       <c r="I431" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>GPG3BD</t>
+          <t>GRK3CQ</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -19361,18 +19357,18 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="E432" t="inlineStr"/>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Introduktion till läraryrket</t>
+          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -19382,19 +19378,19 @@
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>GFI3BU</t>
+          <t>GMN3E2</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -19404,18 +19400,18 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E433" t="inlineStr"/>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Introduktion till existentialismen</t>
+          <t>Dramaturgi, manusskrivande och medieproduktionens villkor</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -19425,19 +19421,19 @@
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E2</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>ABQ2AM</t>
+          <t>GMN3EZ</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -19447,18 +19443,18 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Kreativ kodning</t>
+          <t>Kandidatexamensarbete i Medieproduktion</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -19468,19 +19464,19 @@
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>GPG3CN</t>
+          <t>GMN3EX</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -19490,18 +19486,18 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
+          <t>Alternativa gestaltningsformer</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -19511,19 +19507,19 @@
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>GHI3CP</t>
+          <t>GMN3EY</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -19533,18 +19529,18 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel – inriktning historiedidaktik</t>
+          <t>Vetenskapsteori och metod i Medieproduktion</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -19554,19 +19550,19 @@
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EY</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>GRK3CQ</t>
+          <t>GMN3F2</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -19576,18 +19572,18 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
+          <t>Exponeringsprojekt inom Medieproduktion</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -19597,19 +19593,19 @@
       </c>
       <c r="I437" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>GMN3E2</t>
+          <t>GBQ3FG</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -19619,18 +19615,18 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Dramaturgi, manusskrivande och medieproduktionens villkor</t>
+          <t>Kreativt skrivande</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -19640,19 +19636,19 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>GMN3EZ</t>
+          <t>APG2BF</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -19662,18 +19658,18 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Kandidatexamensarbete i Medieproduktion</t>
+          <t>Att främja en professionsdriven verksamhetsutveckling i förskola, skola och fritidshem</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -19683,19 +19679,19 @@
       </c>
       <c r="I439" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>GMN3EX</t>
+          <t>APG2BK</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -19705,18 +19701,18 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
       <c r="F440" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Alternativa gestaltningsformer</t>
+          <t>Verksamhetsförlagd utbildning 3 - VAL</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -19726,19 +19722,19 @@
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>GMN3EY</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -19748,18 +19744,18 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Vetenskapsteori och metod i Medieproduktion</t>
+          <t>Introduktion till studier i program - VAL</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -19769,19 +19765,19 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>GMN3F2</t>
+          <t>GPG3FS</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -19791,18 +19787,18 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Exponeringsprojekt inom Medieproduktion</t>
+          <t>Verksamhetsförlagd utbildning 1 - VAL</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -19812,19 +19808,19 @@
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>GBQ3FG</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -19834,18 +19830,18 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Kreativt skrivande</t>
+          <t>Verksamhetsförlagd utbildning 2 - VAL</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -19855,19 +19851,19 @@
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>APG2BF</t>
+          <t>GMN3F3</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -19877,18 +19873,18 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E444" t="inlineStr"/>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Att främja en professionsdriven verksamhetsutveckling i förskola, skola och fritidshem</t>
+          <t>Verksamhetsförlagd utbildning inom medieproduktion</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -19898,14 +19894,14 @@
       </c>
       <c r="I444" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F3</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>APG2BK</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -19920,7 +19916,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E445" t="inlineStr"/>
@@ -19931,7 +19927,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 3 - VAL</t>
+          <t>Mentorsutbildning för en kvalitativ introduktionsperiod</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -19941,14 +19937,14 @@
       </c>
       <c r="I445" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GPG3JP</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -19963,7 +19959,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
@@ -19974,7 +19970,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Introduktion till studier i program - VAL</t>
+          <t>Interkulturell och inkluderande undervisning i globala sammanhang</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -19984,313 +19980,12 @@
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" s="2" t="inlineStr">
-        <is>
-          <t>GPG3FS</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="E447" t="inlineStr"/>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>Pedagogiskt arbete</t>
-        </is>
-      </c>
-      <c r="G447" t="inlineStr">
-        <is>
-          <t>Verksamhetsförlagd utbildning 1 - VAL</t>
-        </is>
-      </c>
-      <c r="H447" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I447" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" s="2" t="inlineStr">
-        <is>
-          <t>GPG3FT</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr">
-        <is>
-          <t>Pedagogiskt arbete</t>
-        </is>
-      </c>
-      <c r="G448" t="inlineStr">
-        <is>
-          <t>Verksamhetsförlagd utbildning 2 - VAL</t>
-        </is>
-      </c>
-      <c r="H448" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I448" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" s="2" t="inlineStr">
-        <is>
-          <t>GMN3F3</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>MPR</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="E449" t="inlineStr"/>
-      <c r="F449" t="inlineStr">
-        <is>
-          <t>Medieproduktion</t>
-        </is>
-      </c>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>Verksamhetsförlagd utbildning inom medieproduktion</t>
-        </is>
-      </c>
-      <c r="H449" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I449" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F3</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" s="2" t="inlineStr">
-        <is>
-          <t>APG2CC</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="E450" t="inlineStr"/>
-      <c r="F450" t="inlineStr">
-        <is>
-          <t>Pedagogiskt arbete</t>
-        </is>
-      </c>
-      <c r="G450" t="inlineStr">
-        <is>
-          <t>Mentorsutbildning för en kvalitativ introduktionsperiod</t>
-        </is>
-      </c>
-      <c r="H450" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I450" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" s="2" t="inlineStr">
-        <is>
-          <t>GPG3JP</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="E451" t="inlineStr"/>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>Pedagogiskt arbete</t>
-        </is>
-      </c>
-      <c r="G451" t="inlineStr">
-        <is>
-          <t>Interkulturell och inkluderande undervisning i globala sammanhang</t>
-        </is>
-      </c>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I451" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
         </is>
       </c>
     </row>
-    <row r="452">
-      <c r="A452" s="2" t="inlineStr">
-        <is>
-          <t>GPG3KA</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr"/>
-      <c r="F452" t="inlineStr">
-        <is>
-          <t>Pedagogiskt arbete</t>
-        </is>
-      </c>
-      <c r="G452" t="inlineStr">
-        <is>
-          <t>Didaktik och ledarskap för ämneslärare inriktning årskurs 7-9 (inkl 7,5 hp VFU)</t>
-        </is>
-      </c>
-      <c r="H452" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I452" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KA</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" s="2" t="inlineStr">
-        <is>
-          <t>GPG3KB</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr"/>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>Pedagogiskt arbete</t>
-        </is>
-      </c>
-      <c r="G453" t="inlineStr">
-        <is>
-          <t>Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan (inkl 7,5 hp VFU)</t>
-        </is>
-      </c>
-      <c r="H453" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I453" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KB</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I453"/>
+  <autoFilter ref="A1:I446"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -21182,20 +20877,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I445" r:id="rId888"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A446" r:id="rId889"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I446" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A447" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I447" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A448" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I448" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A449" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I449" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A450" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I450" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A451" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I451" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A452" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I452" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A453" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I453" r:id="rId904"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$446</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$448</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I446"/>
+  <dimension ref="A1:I448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18267,7 +18267,7 @@
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A8</t>
+          <t>GBQ3A9</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Kreativt skrivande</t>
+          <t>Introduktion till att skriva filmadaption</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -18303,14 +18303,14 @@
       </c>
       <c r="I407" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A9</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A9</t>
+          <t>GBQ3AA</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -18336,7 +18336,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Introduktion till att skriva filmadaption</t>
+          <t>Filmhistoria: En introduktion</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -18346,19 +18346,19 @@
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AA</t>
+          <t>GTR3A4</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -18374,12 +18374,12 @@
       <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Filmhistoria: En introduktion</t>
+          <t>Kvantitativ metod</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -18389,19 +18389,19 @@
       </c>
       <c r="I409" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>GTR3A4</t>
+          <t>APG2AB</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -18411,18 +18411,18 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Kvantitativ metod</t>
+          <t>Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -18432,14 +18432,14 @@
       </c>
       <c r="I410" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AB</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>APG2AB</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -18465,7 +18465,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL</t>
+          <t>Rektors pedagogiska ledarskap med fokus på förskolans utbildningsuppdrag</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -18475,14 +18475,14 @@
       </c>
       <c r="I411" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>GPG3AF</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -18508,7 +18508,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Rektors pedagogiska ledarskap med fokus på förskolans utbildningsuppdrag</t>
+          <t>Specialpedagogik och ett läraruppdrag i förändring för ämneslärare årskurs 7–9 - AIL</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -18518,14 +18518,14 @@
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>GPG3AF</t>
+          <t>GPG3AG</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Specialpedagogik och ett läraruppdrag i förändring för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Verksamhetsförlagd utbildning 2 för ämneslärare årskurs 7–9 - AIL</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -18561,19 +18561,19 @@
       </c>
       <c r="I413" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>GPG3AG</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -18583,18 +18583,18 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 2 för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Hårdrock och metal: musikproduktion, kultur och kreativa konventioner</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -18604,19 +18604,19 @@
       </c>
       <c r="I414" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>GAB3AK</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -18626,18 +18626,18 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Hårdrock och metal: musikproduktion, kultur och kreativa konventioner</t>
+          <t>Kommunal styrning och förändringsarbete</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -18647,14 +18647,14 @@
       </c>
       <c r="I415" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AK</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>GAB3AK</t>
+          <t>GAB3AL</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Kommunal styrning och förändringsarbete</t>
+          <t>Ledarskapets juridik</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -18690,19 +18690,19 @@
       </c>
       <c r="I416" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AL</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>GAB3AL</t>
+          <t>GPE3AJ</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -18718,12 +18718,12 @@
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Pedagogik</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Ledarskapets juridik</t>
+          <t>Att leda kollegiala lärprocesser i förskola och skola</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -18733,19 +18733,19 @@
       </c>
       <c r="I417" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>GPE3AJ</t>
+          <t>GLP3AR</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -18755,18 +18755,18 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Pedagogik</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Att leda kollegiala lärprocesser i förskola och skola</t>
+          <t>Ljud- och musikproduktion med Pro Tools</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -18776,19 +18776,19 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>GLP3AR</t>
+          <t>GBQ3AV</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -18798,18 +18798,18 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion med Pro Tools</t>
+          <t>Content för sociala medier</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -18819,14 +18819,14 @@
       </c>
       <c r="I419" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AV</t>
+          <t>GBQ3AW</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Content för sociala medier</t>
+          <t>Explainers med rörlig grafik</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -18862,19 +18862,19 @@
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AW</t>
+          <t>GTR3B6</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -18884,18 +18884,18 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Explainers med rörlig grafik</t>
+          <t>Sälenfjällen - Platsen och besöksnäringen</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -18905,19 +18905,19 @@
       </c>
       <c r="I421" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>GTR3B6</t>
+          <t>GNA3B7</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -18927,18 +18927,18 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Nationalekonomi</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Sälenfjällen - Platsen och besöksnäringen</t>
+          <t>Mikroekonomi, introduktion</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -18948,19 +18948,19 @@
       </c>
       <c r="I422" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B7</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>GNA3B7</t>
+          <t>GRV3BF</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -18970,18 +18970,18 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Nationalekonomi</t>
+          <t>Rättsvetenskap</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Mikroekonomi, introduktion</t>
+          <t>IT-rätt</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -18991,19 +18991,19 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>GBP3BB</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -19013,18 +19013,18 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Rättsvetenskap</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>IT-rätt</t>
+          <t>Fotografiskt bildskapande A</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -19034,14 +19034,14 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BB</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>GBP3BB</t>
+          <t>GBP3BC</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -19067,7 +19067,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Fotografiskt bildskapande A</t>
+          <t>Fotografiskt bildskapande B</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -19077,19 +19077,19 @@
       </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BC</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>GBP3BC</t>
+          <t>GPG3BD</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -19105,12 +19105,12 @@
       <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Fotografiskt bildskapande B</t>
+          <t>Introduktion till läraryrket</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -19120,19 +19120,19 @@
       </c>
       <c r="I426" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>GPG3BD</t>
+          <t>GFI3BU</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -19142,18 +19142,18 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Introduktion till läraryrket</t>
+          <t>Introduktion till existentialismen</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -19163,19 +19163,19 @@
       </c>
       <c r="I427" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>GFI3BU</t>
+          <t>ABQ2AM</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -19185,18 +19185,18 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Introduktion till existentialismen</t>
+          <t>Kreativ kodning</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -19206,19 +19206,19 @@
       </c>
       <c r="I428" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>ABQ2AM</t>
+          <t>GPG3CN</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -19228,18 +19228,18 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Kreativ kodning</t>
+          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -19249,19 +19249,19 @@
       </c>
       <c r="I429" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>GPG3CN</t>
+          <t>GHI3CP</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -19271,18 +19271,18 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
+          <t>Undervisning och lärande genom rollspel – inriktning historiedidaktik</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -19292,19 +19292,19 @@
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>GHI3CP</t>
+          <t>GRK3CQ</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -19320,12 +19320,12 @@
       <c r="E431" t="inlineStr"/>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel – inriktning historiedidaktik</t>
+          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -19335,19 +19335,19 @@
       </c>
       <c r="I431" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>GRK3CQ</t>
+          <t>GMN3E2</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -19357,18 +19357,18 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E432" t="inlineStr"/>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
+          <t>Dramaturgi, manusskrivande och medieproduktionens villkor</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -19378,14 +19378,14 @@
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E2</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>GMN3E2</t>
+          <t>GMN3EZ</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E433" t="inlineStr"/>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Dramaturgi, manusskrivande och medieproduktionens villkor</t>
+          <t>Kandidatexamensarbete i Medieproduktion</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -19421,14 +19421,14 @@
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>GMN3EZ</t>
+          <t>GMN3EX</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
@@ -19454,7 +19454,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Kandidatexamensarbete i Medieproduktion</t>
+          <t>Alternativa gestaltningsformer</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -19464,14 +19464,14 @@
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>GMN3EX</t>
+          <t>GMN3EY</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -19497,7 +19497,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Alternativa gestaltningsformer</t>
+          <t>Vetenskapsteori och metod i Medieproduktion</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -19507,14 +19507,14 @@
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EY</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>GMN3EY</t>
+          <t>GMN3F2</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -19540,7 +19540,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Vetenskapsteori och metod i Medieproduktion</t>
+          <t>Exponeringsprojekt inom Medieproduktion</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -19550,19 +19550,19 @@
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>GMN3F2</t>
+          <t>GBQ3FG</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -19572,18 +19572,18 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Exponeringsprojekt inom Medieproduktion</t>
+          <t>Kreativt skrivande</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -19593,19 +19593,19 @@
       </c>
       <c r="I437" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>GBQ3FG</t>
+          <t>APG2BF</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -19621,12 +19621,12 @@
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Kreativt skrivande</t>
+          <t>Att främja en professionsdriven verksamhetsutveckling i förskola, skola och fritidshem</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -19636,14 +19636,14 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>APG2BF</t>
+          <t>APG2BK</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Att främja en professionsdriven verksamhetsutveckling i förskola, skola och fritidshem</t>
+          <t>Verksamhetsförlagd utbildning 3 - VAL</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -19679,14 +19679,14 @@
       </c>
       <c r="I439" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>APG2BK</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -19712,7 +19712,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 3 - VAL</t>
+          <t>Introduktion till studier i program - VAL</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -19722,14 +19722,14 @@
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GPG3FS</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -19755,7 +19755,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Introduktion till studier i program - VAL</t>
+          <t>Verksamhetsförlagd utbildning 1 - VAL</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -19765,14 +19765,14 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>GPG3FS</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -19798,7 +19798,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 1 - VAL</t>
+          <t>Verksamhetsförlagd utbildning 2 - VAL</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -19808,19 +19808,19 @@
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>GPG3FT</t>
+          <t>GMN3F3</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -19830,18 +19830,18 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 2 - VAL</t>
+          <t>Verksamhetsförlagd utbildning inom medieproduktion</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -19851,19 +19851,19 @@
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F3</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>GMN3F3</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -19873,18 +19873,18 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E444" t="inlineStr"/>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning inom medieproduktion</t>
+          <t>Mentorsutbildning för en kvalitativ introduktionsperiod</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -19894,14 +19894,14 @@
       </c>
       <c r="I444" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>GPG3JP</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E445" t="inlineStr"/>
@@ -19927,7 +19927,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Mentorsutbildning för en kvalitativ introduktionsperiod</t>
+          <t>Interkulturell och inkluderande undervisning i globala sammanhang</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -19937,19 +19937,19 @@
       </c>
       <c r="I445" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>GPG3JP</t>
+          <t>GKG3KD</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -19959,18 +19959,18 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Kulturgeografi</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Interkulturell och inkluderande undervisning i globala sammanhang</t>
+          <t>Geografiska Informationssystem (GIS): Introduktion</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -19980,12 +19980,98 @@
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3KD</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>GKG3KE</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>IKS</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Kulturgeografi</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Geografiska Informationssystem (GIS): Introduktion till GIS-analyser</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3KE</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>GKG3KF</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>IKS</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Kulturgeografi</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Geografiska Informationssystem (GIS): Rumslig analys och statistik</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3KF</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I446"/>
+  <autoFilter ref="A1:I448"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -20877,6 +20963,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I445" r:id="rId888"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A446" r:id="rId889"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I446" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A447" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I447" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A448" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I448" r:id="rId894"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$413</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$411</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I413"/>
+  <dimension ref="A1:I411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15327,12 +15327,12 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>GPG33E</t>
+          <t>AS3001</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -15342,18 +15342,22 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr"/>
+          <t>2014-12-10</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Afrikanska studier</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL</t>
+          <t>Afrikanska studier: Utbildning och förändring i afrikanska samhällen</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -15363,14 +15367,14 @@
       </c>
       <c r="I339" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -15400,7 +15404,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Utbildning och förändring i afrikanska samhällen</t>
+          <t>Afrikanska studier: Afrikanska samhällen i förändring</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -15410,14 +15414,14 @@
       </c>
       <c r="I340" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -15447,7 +15451,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Afrikanska samhällen i förändring</t>
+          <t>Afrikanska studier: Religion och politik i afrikanska samhällen</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -15457,14 +15461,14 @@
       </c>
       <c r="I341" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>AS3004</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -15479,7 +15483,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
+          <t>2015-06-17</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -15494,7 +15498,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Religion och politik i afrikanska samhällen</t>
+          <t>Afrikanska studier: Forskningsprojektets planering</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -15504,19 +15508,19 @@
       </c>
       <c r="I342" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>AS3004</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -15526,22 +15530,18 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2015-06-17</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
+          <t>2023-03-13</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Afrikanska studier</t>
+          <t>Sociologi</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Forskningsprojektets planering</t>
+          <t>Sociologi III</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -15551,19 +15551,19 @@
       </c>
       <c r="I343" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>GAB358</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -15573,18 +15573,18 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Sociologi</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Sociologi III</t>
+          <t>Styrsystem och utveckling i socialtjänst/omsorg</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -15594,19 +15594,19 @@
       </c>
       <c r="I344" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB358</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>GAB358</t>
+          <t>GPA353</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -15622,12 +15622,12 @@
       <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Styrsystem och utveckling i socialtjänst/omsorg</t>
+          <t>Ledarskap</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -15637,14 +15637,14 @@
       </c>
       <c r="I345" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB358</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA353</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>GPA353</t>
+          <t>GPA354</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Ledarskap</t>
+          <t>Arbetsrätt, avtal och förhandling</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -15680,14 +15680,14 @@
       </c>
       <c r="I346" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA353</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>GPA354</t>
+          <t>GPA357</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Arbetsrätt, avtal och förhandling</t>
+          <t>Praktik för personalvetare</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -15723,19 +15723,19 @@
       </c>
       <c r="I347" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA357</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>GPA357</t>
+          <t>GLP359</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -15745,18 +15745,18 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Praktik för personalvetare</t>
+          <t>Dansmusikhistoria och klubbkultur 1: DJ-kulturens utveckling 1970-2000</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -15766,19 +15766,19 @@
       </c>
       <c r="I348" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA357</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>GLP359</t>
+          <t>GFÖ35J</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -15788,18 +15788,18 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Dansmusikhistoria och klubbkultur 1: DJ-kulturens utveckling 1970-2000</t>
+          <t>Turismmarknadsföring</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -15809,19 +15809,19 @@
       </c>
       <c r="I349" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ35J</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>GFÖ35J</t>
+          <t>GBQ35K</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -15831,18 +15831,18 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Turismmarknadsföring</t>
+          <t>Berätta med film om kulturarv och historia</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -15852,19 +15852,19 @@
       </c>
       <c r="I350" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ35J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ35K</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>GBQ35K</t>
+          <t>GEU35L</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -15874,18 +15874,18 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Berätta med film om kulturarv och historia</t>
+          <t>Projektledning I</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -15895,14 +15895,14 @@
       </c>
       <c r="I351" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ35K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35L</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>GEU35L</t>
+          <t>GEU35M</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Projektledning I</t>
+          <t>Entreprenörskap - villkor och särart</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -15938,14 +15938,14 @@
       </c>
       <c r="I352" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35M</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>GEU35M</t>
+          <t>GEU35N</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -15971,7 +15971,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Entreprenörskap - villkor och särart</t>
+          <t>Projektledning II</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -15981,19 +15981,19 @@
       </c>
       <c r="I353" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35N</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>GEU35N</t>
+          <t>GBQ36D</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -16003,18 +16003,18 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Projektledning II</t>
+          <t>Kvalificerad filmproduktion</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -16024,19 +16024,19 @@
       </c>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36D</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>GBQ36D</t>
+          <t>ARK29H</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -16052,12 +16052,12 @@
       <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Kvalificerad filmproduktion</t>
+          <t>Religionsvetenskaplig litteraturkurs</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -16067,19 +16067,19 @@
       </c>
       <c r="I355" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>ARK29H</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -16089,18 +16089,18 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Religionsvetenskaplig litteraturkurs</t>
+          <t>Didaktik och läroplansteori - KPU</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -16110,14 +16110,14 @@
       </c>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -16143,7 +16143,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Didaktik och läroplansteori - KPU</t>
+          <t>Didaktik och läroplansteori</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -16153,19 +16153,19 @@
       </c>
       <c r="I357" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GBQ36K</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -16175,18 +16175,18 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Didaktik och läroplansteori</t>
+          <t>Flerkameraproduktion, fördjupning</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -16196,19 +16196,19 @@
       </c>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>GBQ36K</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -16218,18 +16218,18 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Flerkameraproduktion, fördjupning</t>
+          <t>Historievetenskaplig litteraturkurs</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -16239,14 +16239,14 @@
       </c>
       <c r="I359" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>AHI29R</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Historievetenskaplig litteraturkurs</t>
+          <t>Historievetenskapens teori och metod</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -16282,14 +16282,14 @@
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>AHI29R</t>
+          <t>GHI37M</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E361" t="inlineStr"/>
@@ -16315,7 +16315,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Historievetenskapens teori och metod</t>
+          <t>De nationella minoriteternas samhällshistoria</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -16325,19 +16325,19 @@
       </c>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI37M</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>GHI37M</t>
+          <t>GFI37Z</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -16347,18 +16347,18 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-12-07</t>
         </is>
       </c>
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>De nationella minoriteternas samhällshistoria</t>
+          <t>Gud och bevisen: filosofiska argument för och mot Guds existens</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -16368,19 +16368,19 @@
       </c>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI37M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>GFI37Z</t>
+          <t>GHI38Q</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -16390,18 +16390,18 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2023-12-07</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Gud och bevisen: filosofiska argument för och mot Guds existens</t>
+          <t>Global miljöhistoria</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -16411,19 +16411,19 @@
       </c>
       <c r="I363" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI38Q</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>GHI38Q</t>
+          <t>GBQ38X</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -16433,18 +16433,18 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Global miljöhistoria</t>
+          <t>Fortsätt berätta med film om kulturarv och historia</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -16454,19 +16454,19 @@
       </c>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI38Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>GBQ38X</t>
+          <t>GEU38C</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -16476,18 +16476,18 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Fortsätt berätta med film om kulturarv och historia</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -16497,19 +16497,19 @@
       </c>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU38C</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>GEU38C</t>
+          <t>APG2AA</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -16519,18 +16519,18 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>Lärarskicklighet - utveckling av lärarskicklighet i förskola och skola utifrån forskning</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -16540,19 +16540,19 @@
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU38C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>APG2AA</t>
+          <t>GFÖ39A</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -16562,18 +16562,18 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Lärarskicklighet - utveckling av lärarskicklighet i förskola och skola utifrån forskning</t>
+          <t>Sport Management III</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -16583,19 +16583,19 @@
       </c>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ39A</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>GFÖ39A</t>
+          <t>GBQ3A5</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -16605,18 +16605,18 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Sport Management III</t>
+          <t>Grunderna i filmproduktion</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -16626,14 +16626,14 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ39A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A5</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A5</t>
+          <t>GBQ3A6</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -16659,7 +16659,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Grunderna i filmproduktion</t>
+          <t>Konceptutveckling för korta filmer</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -16669,14 +16669,14 @@
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A6</t>
+          <t>GBQ3A7</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -16702,7 +16702,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Konceptutveckling för korta filmer</t>
+          <t>Star Wars: Film, myter och världar</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -16712,14 +16712,14 @@
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A7</t>
+          <t>GBQ3A9</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Star Wars: Film, myter och världar</t>
+          <t>Introduktion till att skriva filmadaption</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -16755,14 +16755,14 @@
       </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A9</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A9</t>
+          <t>GBQ3AA</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Introduktion till att skriva filmadaption</t>
+          <t>Filmhistoria: En introduktion</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -16798,19 +16798,19 @@
       </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AA</t>
+          <t>GTR3A4</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -16826,12 +16826,12 @@
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Filmhistoria: En introduktion</t>
+          <t>Kvantitativ metod</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -16841,19 +16841,19 @@
       </c>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>GTR3A4</t>
+          <t>APG2AB</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -16863,18 +16863,18 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Kvantitativ metod</t>
+          <t>Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -16884,14 +16884,14 @@
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AB</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>APG2AB</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL</t>
+          <t>Rektors pedagogiska ledarskap med fokus på förskolans utbildningsuppdrag</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -16927,14 +16927,14 @@
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>GPG3AF</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Rektors pedagogiska ledarskap med fokus på förskolans utbildningsuppdrag</t>
+          <t>Specialpedagogik och ett läraruppdrag i förändring för ämneslärare årskurs 7–9 - AIL</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -16970,14 +16970,14 @@
       </c>
       <c r="I376" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>GPG3AF</t>
+          <t>GPG3AG</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -17003,7 +17003,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Specialpedagogik och ett läraruppdrag i förändring för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Verksamhetsförlagd utbildning 2 för ämneslärare årskurs 7–9 - AIL</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -17013,19 +17013,19 @@
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>GPG3AG</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -17035,18 +17035,18 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 2 för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Hårdrock och metal: musikproduktion, kultur och kreativa konventioner</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -17056,19 +17056,19 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>GAB3AK</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -17078,18 +17078,18 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Hårdrock och metal: musikproduktion, kultur och kreativa konventioner</t>
+          <t>Kommunal styrning och förändringsarbete</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -17099,14 +17099,14 @@
       </c>
       <c r="I379" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AK</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>GAB3AK</t>
+          <t>GAB3AL</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Kommunal styrning och förändringsarbete</t>
+          <t>Ledarskapets juridik</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -17142,19 +17142,19 @@
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AL</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>GAB3AL</t>
+          <t>GPE3AJ</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -17170,12 +17170,12 @@
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Pedagogik</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Ledarskapets juridik</t>
+          <t>Att leda kollegiala lärprocesser i förskola och skola</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -17185,19 +17185,19 @@
       </c>
       <c r="I381" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>GPE3AJ</t>
+          <t>GLP3AR</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -17207,18 +17207,18 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Pedagogik</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Att leda kollegiala lärprocesser i förskola och skola</t>
+          <t>Ljud- och musikproduktion med Pro Tools</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -17228,19 +17228,19 @@
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>GLP3AR</t>
+          <t>GBQ3AV</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -17250,18 +17250,18 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion med Pro Tools</t>
+          <t>Content för sociala medier</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -17271,14 +17271,14 @@
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AV</t>
+          <t>GBQ3AW</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Content för sociala medier</t>
+          <t>Explainers med rörlig grafik</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -17314,19 +17314,19 @@
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AW</t>
+          <t>GTR3B6</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -17336,18 +17336,18 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Explainers med rörlig grafik</t>
+          <t>Sälenfjällen - Platsen och besöksnäringen</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -17357,19 +17357,19 @@
       </c>
       <c r="I385" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>GTR3B6</t>
+          <t>GNA3B7</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -17379,18 +17379,18 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Nationalekonomi</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Sälenfjällen - Platsen och besöksnäringen</t>
+          <t>Mikroekonomi, introduktion</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -17400,19 +17400,19 @@
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B7</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>GNA3B7</t>
+          <t>GBP3BB</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -17422,18 +17422,18 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Nationalekonomi</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Mikroekonomi, introduktion</t>
+          <t>Fotografiskt bildskapande A</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -17443,19 +17443,19 @@
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BB</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>GBP3BC</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -17465,18 +17465,18 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Rättsvetenskap</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>IT-rätt</t>
+          <t>Fotografiskt bildskapande B</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -17486,19 +17486,19 @@
       </c>
       <c r="I388" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BC</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>GBP3BB</t>
+          <t>GPG3BD</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -17514,12 +17514,12 @@
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Fotografiskt bildskapande A</t>
+          <t>Introduktion till läraryrket</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -17529,19 +17529,19 @@
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>GBP3BC</t>
+          <t>GFI3BU</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -17551,18 +17551,18 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Fotografiskt bildskapande B</t>
+          <t>Introduktion till existentialismen</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -17572,19 +17572,19 @@
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>GPG3BD</t>
+          <t>ABQ2AM</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -17594,18 +17594,18 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Introduktion till läraryrket</t>
+          <t>Kreativ kodning</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -17615,19 +17615,19 @@
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>GFI3BU</t>
+          <t>GPG3CN</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -17637,18 +17637,18 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Introduktion till existentialismen</t>
+          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -17658,19 +17658,19 @@
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>ABQ2AM</t>
+          <t>GHI3CP</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -17680,18 +17680,18 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Kreativ kodning</t>
+          <t>Undervisning och lärande genom rollspel – inriktning historiedidaktik</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -17701,19 +17701,19 @@
       </c>
       <c r="I393" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>GPG3CN</t>
+          <t>GRK3CQ</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -17723,18 +17723,18 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
+          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -17744,19 +17744,19 @@
       </c>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>GHI3CP</t>
+          <t>GMN3E2</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -17766,18 +17766,18 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel – inriktning historiedidaktik</t>
+          <t>Dramaturgi, manusskrivande och medieproduktionens villkor</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -17787,19 +17787,19 @@
       </c>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E2</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>GRK3CQ</t>
+          <t>GMN3EZ</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -17809,18 +17809,18 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
+          <t>Kandidatexamensarbete i Medieproduktion</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -17830,14 +17830,14 @@
       </c>
       <c r="I396" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>GMN3E2</t>
+          <t>GMN3EX</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -17852,7 +17852,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E397" t="inlineStr"/>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Dramaturgi, manusskrivande och medieproduktionens villkor</t>
+          <t>Alternativa gestaltningsformer</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -17873,14 +17873,14 @@
       </c>
       <c r="I397" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>GMN3EZ</t>
+          <t>GMN3EY</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -17895,7 +17895,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Kandidatexamensarbete i Medieproduktion</t>
+          <t>Vetenskapsteori och metod i Medieproduktion</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -17916,14 +17916,14 @@
       </c>
       <c r="I398" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EY</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>GMN3EX</t>
+          <t>GMN3F2</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -17949,7 +17949,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Alternativa gestaltningsformer</t>
+          <t>Exponeringsprojekt inom Medieproduktion</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -17959,19 +17959,19 @@
       </c>
       <c r="I399" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>GMN3EY</t>
+          <t>GBQ3FG</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -17981,18 +17981,18 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Vetenskapsteori och metod i Medieproduktion</t>
+          <t>Kreativt skrivande</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -18002,19 +18002,19 @@
       </c>
       <c r="I400" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>GMN3F2</t>
+          <t>APG2BF</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -18024,18 +18024,18 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Exponeringsprojekt inom Medieproduktion</t>
+          <t>Att främja en professionsdriven verksamhetsutveckling i förskola, skola och fritidshem</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -18045,19 +18045,19 @@
       </c>
       <c r="I401" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>GBQ3FG</t>
+          <t>APG2BK</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -18067,18 +18067,18 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Kreativt skrivande</t>
+          <t>Verksamhetsförlagd utbildning 3 - VAL</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -18088,14 +18088,14 @@
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>APG2BF</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -18110,7 +18110,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
@@ -18121,7 +18121,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Att främja en professionsdriven verksamhetsutveckling i förskola, skola och fritidshem</t>
+          <t>Introduktion till studier i program - VAL</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -18131,14 +18131,14 @@
       </c>
       <c r="I403" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>APG2BK</t>
+          <t>GPG3FS</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 3 - VAL</t>
+          <t>Verksamhetsförlagd utbildning 1 - VAL</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -18174,14 +18174,14 @@
       </c>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -18207,7 +18207,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Introduktion till studier i program - VAL</t>
+          <t>Verksamhetsförlagd utbildning 2 - VAL</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -18217,19 +18217,19 @@
       </c>
       <c r="I405" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>GPG3FS</t>
+          <t>GMN3F3</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -18239,18 +18239,18 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 1 - VAL</t>
+          <t>Verksamhetsförlagd utbildning inom medieproduktion</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -18260,14 +18260,14 @@
       </c>
       <c r="I406" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F3</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>GPG3FT</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -18282,7 +18282,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E407" t="inlineStr"/>
@@ -18293,7 +18293,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 2 - VAL</t>
+          <t>Mentorsutbildning för en kvalitativ introduktionsperiod</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -18303,19 +18303,19 @@
       </c>
       <c r="I407" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>GMN3F3</t>
+          <t>GPG3JP</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -18325,18 +18325,18 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E408" t="inlineStr"/>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning inom medieproduktion</t>
+          <t>Interkulturell och inkluderande undervisning i globala sammanhang</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -18346,19 +18346,19 @@
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>GKG3KD</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -18368,18 +18368,18 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Kulturgeografi</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Mentorsutbildning för en kvalitativ introduktionsperiod</t>
+          <t>Geografiska Informationssystem (GIS): Introduktion</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -18389,19 +18389,19 @@
       </c>
       <c r="I409" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3KD</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>GPG3JP</t>
+          <t>GKG3KE</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -18411,18 +18411,18 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Kulturgeografi</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Interkulturell och inkluderande undervisning i globala sammanhang</t>
+          <t>Geografiska Informationssystem (GIS): Introduktion till GIS-analyser</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -18432,14 +18432,14 @@
       </c>
       <c r="I410" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3KE</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>GKG3KD</t>
+          <t>GKG3KF</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -18465,7 +18465,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Geografiska Informationssystem (GIS): Introduktion</t>
+          <t>Geografiska Informationssystem (GIS): Rumslig analys och statistik</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -18475,98 +18475,12 @@
       </c>
       <c r="I411" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3KD</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" s="2" t="inlineStr">
-        <is>
-          <t>GKG3KE</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>KGA</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>Kulturgeografi</t>
-        </is>
-      </c>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>Geografiska Informationssystem (GIS): Introduktion till GIS-analyser</t>
-        </is>
-      </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I412" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3KE</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" s="2" t="inlineStr">
-        <is>
-          <t>GKG3KF</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>KGA</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>Kulturgeografi</t>
-        </is>
-      </c>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>Geografiska Informationssystem (GIS): Rumslig analys och statistik</t>
-        </is>
-      </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I413" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3KF</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I413"/>
+  <autoFilter ref="A1:I411"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -19388,10 +19302,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I410" r:id="rId818"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A411" r:id="rId819"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I411" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A412" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I412" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A413" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I413" r:id="rId824"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$412</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$408</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I412"/>
+  <dimension ref="A1:I408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8656,12 +8656,12 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>PG3065</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8677,12 +8677,12 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i pedagogiskt arbete</t>
+          <t>Verksamhetsförlagt projektarbete i Turismvetenskap</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -8692,19 +8692,19 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>TR1034</t>
+          <t>BQ2057</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8714,18 +8714,18 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2017-03-09</t>
+          <t>2017-03-22</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagt projektarbete i Turismvetenskap</t>
+          <t>Fördjupning i klippning för film/TV</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -8735,19 +8735,19 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2057</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>BQ2057</t>
+          <t>TR1035</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8757,18 +8757,18 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2017-03-22</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Fördjupning i klippning för film/TV</t>
+          <t>Internationella evenemang och festivaler</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -8778,19 +8778,19 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2057</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>TR1035</t>
+          <t>AB1031</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -8800,18 +8800,18 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2017-09-21</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Internationella evenemang och festivaler</t>
+          <t>Professionell utveckling - genom fokus på kollektivt lärande</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -8821,19 +8821,19 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1031</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>AB1031</t>
+          <t>EU1036</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8849,12 +8849,12 @@
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Professionell utveckling - genom fokus på kollektivt lärande</t>
+          <t>Affärsplanering</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -8864,14 +8864,14 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1036</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>EU1036</t>
+          <t>EU1037</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8907,19 +8907,19 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1037</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>EU1037</t>
+          <t>AS3014</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -8929,18 +8929,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2017-09-26</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Affärsplanering</t>
+          <t>Afrikanska studier: Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -8950,14 +8950,14 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3014</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>AS3014</t>
+          <t>AS3015</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv</t>
+          <t>Afrikanska studier: Mänskliga rättigheter och demokrati i Afrika söder om Sahara</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -8993,14 +8993,14 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3015</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>AS3015</t>
+          <t>AS3016</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Mänskliga rättigheter och demokrati i Afrika söder om Sahara</t>
+          <t>Afrikanska studier: Islam och islamiska samhällen i Afrika</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -9036,14 +9036,14 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3016</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>AS3016</t>
+          <t>AS3017</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Islam och islamiska samhällen i Afrika</t>
+          <t>Afrikanska studier: Litteratur och politik i det samtida Afrika</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9079,14 +9079,14 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>AS3017</t>
+          <t>AS4005</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Litteratur och politik i det samtida Afrika</t>
+          <t>Afrikanska studier: Examensarbete för masterexamen</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9122,19 +9122,19 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4005</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>AS4005</t>
+          <t>BQ2058</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -9144,18 +9144,18 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2017-09-26</t>
+          <t>2017-12-08</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Examensarbete för masterexamen</t>
+          <t>Manus för TV och film 4. TV-format och klassiskt berättande</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9165,19 +9165,19 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2058</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>BQ2058</t>
+          <t>AB1032</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -9187,18 +9187,18 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2017-12-08</t>
+          <t>2018-01-25</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Manus för TV och film 4. TV-format och klassiskt berättande</t>
+          <t>Personligt ledarskap</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9208,14 +9208,14 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1032</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>AB1032</t>
+          <t>AB1033</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Personligt ledarskap</t>
+          <t>Bemöta, bedöma, berika: Ett normkritiskt perspektiv på genus och mångfald för utveckling och innovation i företag</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9251,19 +9251,19 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1033</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>AB1033</t>
+          <t>FPA0002</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -9273,18 +9273,18 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2018-01-25</t>
+          <t>2018-02-15</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Bemöta, bedöma, berika: Ett normkritiskt perspektiv på genus och mångfald för utveckling och innovation i företag</t>
+          <t>Forskning och pedagogisk praktik - kommunikation, kunskap och samverkan</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9294,19 +9294,19 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0002</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>FPA0002</t>
+          <t>TR1036</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -9316,18 +9316,18 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2018-02-15</t>
+          <t>2018-03-08</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Forskning och pedagogisk praktik - kommunikation, kunskap och samverkan</t>
+          <t>Turismteori och praxis</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9337,19 +9337,19 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>TR1036</t>
+          <t>FPA0004</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -9359,18 +9359,18 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2018-03-08</t>
+          <t>2018-03-28</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Turismteori och praxis</t>
+          <t>Det demokratiska värdegrundsuppdraget i komplexa skolpraktiker</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9380,14 +9380,14 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0004</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>FPA0004</t>
+          <t>FPA0006</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Det demokratiska värdegrundsuppdraget i komplexa skolpraktiker</t>
+          <t>Introduktion till forskning i pedagogiskt arbete</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9423,19 +9423,19 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0006</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>FPA0006</t>
+          <t>GBQ22U</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9445,18 +9445,18 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2018-03-28</t>
+          <t>2018-04-25</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Introduktion till forskning i pedagogiskt arbete</t>
+          <t>Kvalificerad filmproduktion</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -9466,19 +9466,19 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ22U</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GBQ22U</t>
+          <t>GRV22R</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9488,18 +9488,18 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2018-04-25</t>
+          <t>2018-04-26</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Rättsvetenskap</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Kvalificerad filmproduktion</t>
+          <t>Dataskyddsjuridik</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -9509,19 +9509,19 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ22U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GRV22R</t>
+          <t>FI1023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9531,18 +9531,22 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr"/>
+          <t>2006-10-19</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Rättsvetenskap</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Dataskyddsjuridik</t>
+          <t>Filosofi och vetenskapsteori</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9552,19 +9556,19 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>FI1023</t>
+          <t>GAB24E</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9574,22 +9578,18 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2006-10-19</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>2018-07-01</t>
-        </is>
-      </c>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Filosofi och vetenskapsteori</t>
+          <t>Att vara ledare</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9599,14 +9599,14 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB24E</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GAB24E</t>
+          <t>GAB24F</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Att vara ledare</t>
+          <t>Arbetsmiljöarbete - i praktiken</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -9642,19 +9642,19 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB24F</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GAB24F</t>
+          <t>GBQ24C</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9670,12 +9670,12 @@
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Arbetsmiljöarbete - i praktiken</t>
+          <t>Berätta med film om kulturarv och historia</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -9685,19 +9685,19 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB24F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ24C</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GBQ24C</t>
+          <t>HI2016</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9707,18 +9707,22 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
+          <t>2016-05-18</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
           <t>2018-09-13</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Berätta med film om kulturarv och historia</t>
+          <t>Historia III</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9728,14 +9732,14 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ24C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>HI2016</t>
+          <t>HI2017</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -9765,7 +9769,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Historia III</t>
+          <t>Historia III, inklusive examensarbete för kandidatexamen</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -9775,19 +9779,19 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2017</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>HI2017</t>
+          <t>BQ2018</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9797,22 +9801,22 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2016-05-18</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Historia III, inklusive examensarbete för kandidatexamen</t>
+          <t>Manus för TV och film 5. Gestaltning och filmiskt berättande</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9822,19 +9826,19 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>BQ2018</t>
+          <t>RK1068</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9844,22 +9848,22 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2016-09-13</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2018-12-10</t>
+          <t>2018-12-21</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Manus för TV och film 5. Gestaltning och filmiskt berättande</t>
+          <t>Religionsvetenskap II: Forskningsplan för fältarbete</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -9869,19 +9873,19 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>RK1068</t>
+          <t>GAB26D</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9891,22 +9895,18 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2016-09-13</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>2018-12-21</t>
-        </is>
-      </c>
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Religionsvetenskap II: Forskningsplan för fältarbete</t>
+          <t>Ny som chef</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9916,19 +9916,19 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB26D</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GAB26D</t>
+          <t>GBQ27K</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9938,18 +9938,18 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2019-03-04</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Ny som chef</t>
+          <t>Manus för TV och film 1. Filmberättandets grundelement och gestaltning</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -9959,19 +9959,19 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB26D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ27K</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GBQ27K</t>
+          <t>GPG27X</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9981,18 +9981,18 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2019-03-04</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Manus för TV och film 1. Filmberättandets grundelement och gestaltning</t>
+          <t>Lärares ledarskap</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -10002,19 +10002,19 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ27K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GPG27X</t>
+          <t>FI1034</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -10024,18 +10024,22 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr"/>
+          <t>2010-02-16</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>2019-03-18</t>
+        </is>
+      </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lärares ledarskap</t>
+          <t>Filosofi II</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -10045,19 +10049,19 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1034</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>FI1034</t>
+          <t>HI1015</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -10067,22 +10071,22 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2010-02-16</t>
+          <t>2013-03-11</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2019-03-18</t>
+          <t>2019-03-27</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Filosofi II</t>
+          <t>Historia II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10092,19 +10096,19 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1015</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>HI1015</t>
+          <t>GBQ29D</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -10114,22 +10118,18 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2013-03-11</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>2019-03-27</t>
-        </is>
-      </c>
+          <t>2019-05-03</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Historia II med didaktisk inriktning</t>
+          <t>Flerkameraproduktion, fördjupning</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10139,14 +10139,14 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29D</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GBQ29D</t>
+          <t>GBQ29E</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Flerkameraproduktion, fördjupning</t>
+          <t>Exponeringsprojekt i bildproduktion</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -10182,19 +10182,19 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>GBQ29E</t>
+          <t>GHI29Y</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -10204,18 +10204,18 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2019-05-03</t>
+          <t>2019-06-17</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Exponeringsprojekt i bildproduktion</t>
+          <t>Historia III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -10225,19 +10225,19 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>GHI29Y</t>
+          <t>GLP29V</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -10253,12 +10253,12 @@
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Historia III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Musikproduktionsanalys</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10268,19 +10268,19 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29V</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>GLP29V</t>
+          <t>FPA0005</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -10290,18 +10290,18 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Musikproduktionsanalys</t>
+          <t>Forskning och pedagogisk praktik– teoretiska perspektiv</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -10311,19 +10311,19 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0005</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>FPA0005</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -10333,18 +10333,22 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr"/>
+          <t>2018-11-15</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Statsvetenskap</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Forskning och pedagogisk praktik– teoretiska perspektiv</t>
+          <t>Samhällsvetenskapliga metoder III - inriktning statsvetenskap</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -10354,19 +10358,19 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>GAB2AJ</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -10376,22 +10380,18 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Statsvetenskap</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Samhällsvetenskapliga metoder III - inriktning statsvetenskap</t>
+          <t>Att vara ledare</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -10401,19 +10401,19 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2AJ</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GAB2AJ</t>
+          <t>GBQ2AY</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -10423,18 +10423,18 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2019-08-29</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Att vara ledare</t>
+          <t>Digital efterbearbetning av ljud och bild</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -10444,14 +10444,14 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2AY</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GBQ2AY</t>
+          <t>GBQ2AZ</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Digital efterbearbetning av ljud och bild</t>
+          <t>Ljussättning och färgkorrigering inom filmdesign</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -10487,19 +10487,19 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2AY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2AZ</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GBQ2AZ</t>
+          <t>GFÖ2B9</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -10515,12 +10515,12 @@
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Ljussättning och färgkorrigering inom filmdesign</t>
+          <t>Ledarskap och organisationsbeteende</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -10530,19 +10530,19 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2AZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ2B9</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GFÖ2B9</t>
+          <t>FPA2227</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -10552,18 +10552,18 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2019-09-23</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Ledarskap och organisationsbeteende</t>
+          <t>Lärares ledarskap - villkor och praktik</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -10573,19 +10573,19 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ2B9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>FPA2227</t>
+          <t>GLP2BQ</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -10595,18 +10595,18 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2019-09-23</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Lärares ledarskap - villkor och praktik</t>
+          <t>Medieproduktion som projektarbete</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -10616,19 +10616,19 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2BQ</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GLP2BQ</t>
+          <t>FPA2226</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -10638,18 +10638,18 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
+          <t>2019-10-23</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Medieproduktion som projektarbete</t>
+          <t>Läsinlärning och läsutveckling i teori och praktik</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -10659,19 +10659,19 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>FPA2226</t>
+          <t>GEU2CA</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -10681,18 +10681,18 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2019-10-23</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Läsinlärning och läsutveckling i teori och praktik</t>
+          <t>Det entreprenöriella företagets förutsättningar</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -10702,14 +10702,14 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CA</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GEU2CA</t>
+          <t>GEU2CB</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Det entreprenöriella företagets förutsättningar</t>
+          <t>Ledarskap och grupprocesser</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -10745,19 +10745,19 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CB</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GEU2CB</t>
+          <t>GRV2CE</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -10773,12 +10773,12 @@
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Rättsvetenskap</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Ledarskap och grupprocesser</t>
+          <t>Småföretagens regelverk</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -10788,19 +10788,19 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GRV2CE</t>
+          <t>GAB2CC</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -10810,18 +10810,18 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2019-11-28</t>
+          <t>2019-12-02</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Rättsvetenskap</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Småföretagens regelverk</t>
+          <t>Ny som ledare</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -10831,19 +10831,19 @@
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2CC</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>GAB2CC</t>
+          <t>FPA0003</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -10853,18 +10853,22 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2019-12-02</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr"/>
+          <t>2018-03-28</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>2019-12-18</t>
+        </is>
+      </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Ny som ledare</t>
+          <t>Akademiskt skrivande och talande  på engelska</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -10874,19 +10878,19 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0003</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>FPA0003</t>
+          <t>GHI2CK</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -10896,22 +10900,18 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2018-03-28</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>2019-12-18</t>
-        </is>
-      </c>
+          <t>2020-01-30</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Akademiskt skrivande och talande  på engelska</t>
+          <t>Introduktion till svensk kultur och samhälle</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -10921,14 +10921,14 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CK</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>GHI2CK</t>
+          <t>GHI2CN</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Introduktion till svensk kultur och samhälle</t>
+          <t>Historia I</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -10964,14 +10964,14 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CN</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>GHI2CN</t>
+          <t>GHI2CP</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Historia I</t>
+          <t>Historia I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -11007,14 +11007,14 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CP</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>GHI2CP</t>
+          <t>GHI2CQ</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Historia I med didaktisk inriktning</t>
+          <t>Historia II</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -11050,14 +11050,14 @@
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CQ</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GHI2CQ</t>
+          <t>GHI2CR</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Historia II</t>
+          <t>Historia II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -11093,19 +11093,19 @@
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CR</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>GHI2CR</t>
+          <t>GLP2CX</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -11115,18 +11115,18 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2020-01-30</t>
+          <t>2020-01-31</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Historia II med didaktisk inriktning</t>
+          <t>Musikskapande</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -11136,19 +11136,19 @@
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2CX</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GLP2CX</t>
+          <t>GKG2CS</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -11158,18 +11158,18 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2020-01-31</t>
+          <t>2020-02-06</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Kulturgeografi</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Musikskapande</t>
+          <t>Marknadsanalyser med hjälp av GIS</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -11179,19 +11179,19 @@
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2CX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG2CS</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GKG2CS</t>
+          <t>GBQ2EB</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -11201,18 +11201,18 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2020-02-06</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Kulturgeografi</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Marknadsanalyser med hjälp av GIS</t>
+          <t>Fakta, fiktion och flerkameraproduktion</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -11222,14 +11222,14 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG2CS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2EB</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GBQ2EB</t>
+          <t>GBQ2EC</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Fakta, fiktion och flerkameraproduktion</t>
+          <t>Fortsätt berätta med film om kulturarv och historia</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -11265,19 +11265,19 @@
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2EB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2EC</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GBQ2EC</t>
+          <t>GFÖ2FF</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -11287,18 +11287,18 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Fortsätt berätta med film om kulturarv och historia</t>
+          <t>Vetenskap och metod I</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -11308,19 +11308,19 @@
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2EC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ2FF</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>GFÖ2FF</t>
+          <t>GPA2FL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -11330,18 +11330,18 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-03-09</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Vetenskap och metod I</t>
+          <t>Samspel i organisationen - gruppen</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -11351,19 +11351,19 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ2FF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>GPA2FL</t>
+          <t>GHI2FU</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -11373,18 +11373,18 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2020-03-09</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Samspel i organisationen - gruppen</t>
+          <t>Introduktion till afrikastudier</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -11394,19 +11394,19 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2FU</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>GHI2FU</t>
+          <t>FPA222A</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -11416,18 +11416,18 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Introduktion till afrikastudier</t>
+          <t>Vetenskapsteori och forskningsetik</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -11437,14 +11437,14 @@
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222A</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>FPA222A</t>
+          <t>FPA2228</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2020-06-09</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Vetenskapsteori och forskningsetik</t>
+          <t>Introduktion till forskning i pedagogiskt arbete</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -11480,19 +11480,19 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2228</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>FPA2228</t>
+          <t>GBQ2HC</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -11502,18 +11502,18 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2020-06-09</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Introduktion till forskning i pedagogiskt arbete</t>
+          <t>Introduktion till produktion av rörlig bild för Manus för film och TV</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -11523,14 +11523,14 @@
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2HC</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>GBQ2HC</t>
+          <t>GBQ2HD</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Introduktion till produktion av rörlig bild för Manus för film och TV</t>
+          <t>Grunderna i filmproduktion för Manus för film och TV</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -11566,19 +11566,19 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2HC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2HD</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>GBQ2HD</t>
+          <t>FI1038</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -11588,18 +11588,22 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr"/>
+          <t>2010-10-19</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Grunderna i filmproduktion för Manus för film och TV</t>
+          <t>Samhällsvetenskapernas vetenskapsteori</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -11609,19 +11613,19 @@
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2HD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1038</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>FI1038</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -11631,7 +11635,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2010-10-19</t>
+          <t>2015-12-10</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -11641,12 +11645,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Samhällsvetenskapernas vetenskapsteori</t>
+          <t>Från idé till master</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -11656,19 +11660,19 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>FI1026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -11678,22 +11682,22 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2015-12-10</t>
+          <t>2006-10-19</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Från idé till master</t>
+          <t>Filosofi: Moralfilosofi</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -11703,14 +11707,14 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1026</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>FI1026</t>
+          <t>FI1035</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -11725,7 +11729,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2006-10-19</t>
+          <t>2010-02-16</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -11740,7 +11744,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Filosofi: Moralfilosofi</t>
+          <t>Filosofi: 1900-talets filosofi</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -11750,14 +11754,14 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1035</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>FI1035</t>
+          <t>FI1036</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -11787,7 +11791,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Filosofi: 1900-talets filosofi</t>
+          <t>Filosofi: Politisk filosofi</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -11797,14 +11801,14 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1036</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>FI1036</t>
+          <t>FI1037</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -11834,7 +11838,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Filosofi: Politisk filosofi</t>
+          <t>Filosofi: Filosofiska klassiker</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -11844,14 +11848,14 @@
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1037</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>FI1037</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -11866,7 +11870,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2010-02-16</t>
+          <t>2011-05-30</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -11881,7 +11885,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Filosofi: Filosofiska klassiker</t>
+          <t>Materialvetenskapens idéhistoria och vetenskapsteori</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -11891,19 +11895,19 @@
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>HI1004</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -11913,7 +11917,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2011-05-30</t>
+          <t>2007-01-09</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -11923,12 +11927,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Materialvetenskapens idéhistoria och vetenskapsteori</t>
+          <t>Introduktion till svensk kultur och samhälle</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -11938,14 +11942,14 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1004</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>HI1004</t>
+          <t>HI1006</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -11960,7 +11964,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2007-01-09</t>
+          <t>2009-05-28</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -11975,7 +11979,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Introduktion till svensk kultur och samhälle</t>
+          <t>Globala rörelser för social rättvisa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -11985,19 +11989,19 @@
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1006</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>HI1006</t>
+          <t>FI1024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -12007,22 +12011,22 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2009-05-28</t>
+          <t>2006-10-19</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2020-07-06</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Globala rörelser för social rättvisa</t>
+          <t>Filosofi: Två teman inom filosofi</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -12032,14 +12036,14 @@
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>FI1024</t>
+          <t>FI2003</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -12054,7 +12058,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2006-10-19</t>
+          <t>2010-02-16</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -12069,7 +12073,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Filosofi: Två teman inom filosofi</t>
+          <t>Filosofi: Filosofi III</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -12079,19 +12083,19 @@
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>SK1062</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -12101,22 +12105,22 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2010-02-16</t>
+          <t>2015-04-09</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2020-07-06</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Statsvetenskap</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Filosofi: Filosofi III</t>
+          <t>Förvaltning i Sverige och EU</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -12126,19 +12130,19 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>SK1062</t>
+          <t>AHI263</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -12148,22 +12152,18 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2015-04-09</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Statsvetenskap</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Förvaltning i Sverige och EU</t>
+          <t>Afrikanska studier: Islam och islamiska samhällen i Afrika</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -12173,19 +12173,19 @@
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI263</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>AHI263</t>
+          <t>GPA2K3</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -12195,18 +12195,18 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Islam och islamiska samhällen i Afrika</t>
+          <t>Marknadsföring för personalvetare</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -12216,19 +12216,19 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI263</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>GPA2K3</t>
+          <t>GRK2KL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -12238,18 +12238,18 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Marknadsföring för personalvetare</t>
+          <t>Mänskliga rättigheter: Examensarbete för kandidatexamen</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -12259,19 +12259,19 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>GRK2KL</t>
+          <t>GEU2KV</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -12281,18 +12281,18 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Mänskliga rättigheter: Examensarbete för kandidatexamen</t>
+          <t>Entreprenörskap i regional utveckling och tillväxt</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -12302,14 +12302,14 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>GEU2KV</t>
+          <t>GEU2KW</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Entreprenörskap i regional utveckling och tillväxt</t>
+          <t>Entreprenörskapets teoretiska klassiker</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -12345,14 +12345,14 @@
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KW</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>GEU2KW</t>
+          <t>GEU2KX</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Entreprenörskapets teoretiska klassiker</t>
+          <t>Innovation A</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -12388,19 +12388,19 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KX</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>GEU2KX</t>
+          <t>GPA2KU</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -12416,12 +12416,12 @@
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Innovation A</t>
+          <t>Implementering av hållbar strategisk styrning</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -12431,19 +12431,19 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>GPA2KU</t>
+          <t>APG26D</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -12459,12 +12459,12 @@
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Implementering av hållbar strategisk styrning</t>
+          <t>Didaktisk analys för fortsatt professionsutveckling</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -12474,19 +12474,19 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>APG26D</t>
+          <t>FPA222B</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="E273" t="inlineStr"/>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Didaktisk analys för fortsatt professionsutveckling</t>
+          <t>Vetenskapliga metoder</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -12517,14 +12517,14 @@
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222B</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>FPA222B</t>
+          <t>FPA0007</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -12539,10 +12539,14 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2020-12-02</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr"/>
+          <t>2018-05-30</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>2020-12-16</t>
+        </is>
+      </c>
       <c r="F274" t="inlineStr">
         <is>
           <t>Pedagogiskt arbete</t>
@@ -12550,7 +12554,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Vetenskapliga metoder</t>
+          <t>Intellektuella utmaningar -  att designa och kommunicera ett forskningsprojekt</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -12560,19 +12564,19 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>FPA0007</t>
+          <t>GPA2LM</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -12582,22 +12586,18 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2018-05-30</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>2020-12-16</t>
-        </is>
-      </c>
+          <t>2021-01-28</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Intellektuella utmaningar -  att designa och kommunicera ett forskningsprojekt</t>
+          <t>Personal och arbetsliv - en introduktion</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -12607,14 +12607,14 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>GPA2LM</t>
+          <t>GPA2LN</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv - en introduktion</t>
+          <t>Ekonomi- och verksamhetsstyrning för personalvetare</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -12650,19 +12650,19 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>GPA2LN</t>
+          <t>FPA222C</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -12672,18 +12672,18 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-02-02</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Ekonomi- och verksamhetsstyrning för personalvetare</t>
+          <t>Praktikutvecklande forskningsansatser för undervisning och lärande</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -12693,19 +12693,19 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222C</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>FPA222C</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -12715,18 +12715,18 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Rättsvetenskap</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Praktikutvecklande forskningsansatser för undervisning och lärande</t>
+          <t>Småföretagens regelverk I</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -12736,19 +12736,19 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>AHI26P</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -12758,18 +12758,18 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Rättsvetenskap</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Småföretagens regelverk I</t>
+          <t>Afrikanska studier: Islam och islamiska samhällen i Afrika</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -12779,19 +12779,19 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI26P</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>AHI26P</t>
+          <t>GBQ2MT</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -12801,18 +12801,18 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Islam och islamiska samhällen i Afrika</t>
+          <t>Dokumentärfilmproduktion</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -12822,19 +12822,19 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI26P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2MT</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>GBQ2MT</t>
+          <t>GAB2P6</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -12844,18 +12844,18 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Dokumentärfilmproduktion</t>
+          <t>Professionell distanskommunikation</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -12865,19 +12865,19 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2MT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2P6</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>GAB2P6</t>
+          <t>GNA2NT</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -12893,12 +12893,12 @@
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Nationalekonomi</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Professionell distanskommunikation</t>
+          <t>Finansiella marknader och penningpolitik</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -12908,19 +12908,19 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2P6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>GNA2NT</t>
+          <t>GPA2P7</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -12936,12 +12936,12 @@
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Nationalekonomi</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Finansiella marknader och penningpolitik</t>
+          <t>Samhällsvetenskaplig metod och vetenskapsteori II</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -12951,19 +12951,19 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>GPA2P7</t>
+          <t>GBQ2NH</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -12973,18 +12973,18 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Samhällsvetenskaplig metod och vetenskapsteori II</t>
+          <t>Projektplanering och användarperspektiv</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -12994,14 +12994,14 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NH</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GBQ2NH</t>
+          <t>GBQ2NM</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Projektplanering och användarperspektiv</t>
+          <t>Vetenskapsteori och metod i Bildproduktion</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -13037,14 +13037,14 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NM</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GBQ2NM</t>
+          <t>GBQ2NP</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Vetenskapsteori och metod i Bildproduktion</t>
+          <t>Kandidatexamensarbete i Bildproduktion</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -13080,19 +13080,19 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NP</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>GBQ2NP</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -13108,12 +13108,12 @@
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Kandidatexamensarbete i Bildproduktion</t>
+          <t>Kabbala och judisk mystik från antiken till modern tid</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -13123,19 +13123,19 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>FPA222D</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -13145,18 +13145,18 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Kabbala och judisk mystik från antiken till modern tid</t>
+          <t>Språklig mångfald i utbildningssammanhang</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -13166,19 +13166,19 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222D</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>FPA222D</t>
+          <t>GPG2N7</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -13188,10 +13188,14 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
           <t>2021-03-15</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
           <t>Pedagogiskt arbete</t>
@@ -13199,7 +13203,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Språklig mångfald i utbildningssammanhang</t>
+          <t>Skolväsendets historia</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -13209,19 +13213,19 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>GPG2N7</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -13231,22 +13235,18 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>2021-03-15</t>
-        </is>
-      </c>
+          <t>2021-03-18</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Skolväsendets historia</t>
+          <t>Religionsvetenskap III med didaktisk inriktning för gymnasieskolan</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -13256,19 +13256,19 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -13278,18 +13278,18 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Statsvetenskap</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Religionsvetenskap III med didaktisk inriktning för gymnasieskolan</t>
+          <t>Examensarbete för högskoleexamen i statsvetenskap</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -13299,14 +13299,14 @@
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Examensarbete för högskoleexamen i statsvetenskap</t>
+          <t>Examensarbete för kandidatexamen i statsvetenskap</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -13342,19 +13342,19 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>FPA222E</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -13364,18 +13364,18 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-05-04</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Statsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i statsvetenskap</t>
+          <t>Intellektuella utmaningar – att formulera och undersöka ett problem</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -13385,14 +13385,14 @@
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>FPA222E</t>
+          <t>FPA222F</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Intellektuella utmaningar – att formulera och undersöka ett problem</t>
+          <t>Akademiskt skrivande och talande på engelska</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -13428,14 +13428,14 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222F</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>FPA222F</t>
+          <t>FPA222G</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Akademiskt skrivande och talande på engelska</t>
+          <t>Forskningskommunikation för samhällsutveckling</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -13471,19 +13471,19 @@
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>FPA222G</t>
+          <t>GBQ2QB</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -13493,18 +13493,18 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2021-05-04</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Forskningskommunikation för samhällsutveckling</t>
+          <t>Kvalificerat filmmanusprojekt</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -13514,19 +13514,19 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2QB</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GBQ2QB</t>
+          <t>GLP2QX</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -13536,18 +13536,18 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Kvalificerat filmmanusprojekt</t>
+          <t>Möten med skilda musikgenrer</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -13557,19 +13557,19 @@
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2QB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GLP2QX</t>
+          <t>GEU2QY</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -13579,18 +13579,18 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Möten med skilda musikgenrer</t>
+          <t>Ledarskap</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -13600,19 +13600,19 @@
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2QY</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>GEU2QY</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -13622,18 +13622,18 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Ledarskap</t>
+          <t>Kompetensförsörjning - avveckling och förändring</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -13643,19 +13643,19 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2QY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -13671,12 +13671,12 @@
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Kompetensförsörjning - avveckling och förändring</t>
+          <t>Religionsvetenskap III: Uppsats</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -13686,14 +13686,14 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Religionsvetenskap III: Uppsats</t>
+          <t>Religionsvetenskap III: Examensarbete för kandidatexamen</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -13729,19 +13729,19 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>SO1019</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -13751,18 +13751,22 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
+          <t>2010-10-19</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Sociologi</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Religionsvetenskap III: Examensarbete för kandidatexamen</t>
+          <t>Introduktion till samhällsvetenskap</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -13772,19 +13776,19 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>GAB2S5</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -13794,22 +13798,18 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2010-10-19</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
+          <t>2021-11-16</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Sociologi</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Introduktion till samhällsvetenskap</t>
+          <t>Arbetsmiljö</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -13819,19 +13819,19 @@
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2S5</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>GNA2RY</t>
+          <t>GPE2SA</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -13841,18 +13841,18 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Nationalekonomi</t>
+          <t>Pedagogik</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Statistik för ekonomer</t>
+          <t>Utbildningssystemet i Sverige</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -13862,19 +13862,19 @@
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2RY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE2SA</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>GAB2S5</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -13884,18 +13884,18 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Arbetsmiljö</t>
+          <t>Samhällsorienterande ämnen, årskurs 4-6</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -13905,19 +13905,19 @@
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2S5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>GPE2SA</t>
+          <t>GAB2TR</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -13927,18 +13927,18 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2021-12-03</t>
+          <t>2021-12-07</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Pedagogik</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Utbildningssystemet i Sverige</t>
+          <t>Förståelse och förhållningssätt för främjande av utvecklingsprocesser</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -13948,14 +13948,14 @@
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE2SA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2TR</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG2SG</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2021-12-03</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="E307" t="inlineStr"/>
@@ -13981,7 +13981,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Samhällsorienterande ämnen, årskurs 4-6</t>
+          <t>Omsorg, relationer och etik i förskolläraryrket</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -13991,19 +13991,19 @@
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>GAB2TR</t>
+          <t>GPG2SH</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -14013,18 +14013,18 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2021-12-07</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Förståelse och förhållningssätt för främjande av utvecklingsprocesser</t>
+          <t>Lek i förskolan (varav 7,5 hp VFU)</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -14034,14 +14034,14 @@
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB2TR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>GPG2SG</t>
+          <t>GPG2TT</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="E309" t="inlineStr"/>
@@ -14077,19 +14077,19 @@
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>GPG2SH</t>
+          <t>GBQ2U3</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -14099,18 +14099,18 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Lek i förskolan (varav 7,5 hp VFU)</t>
+          <t>Människan och den rörliga bilden</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -14120,19 +14120,19 @@
       </c>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U3</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>GPG2TT</t>
+          <t>GBQ2U4</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -14142,18 +14142,18 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2021-12-22</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Omsorg, relationer och etik i förskolläraryrket</t>
+          <t>Informationsfilmsproduktion</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -14163,14 +14163,14 @@
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U4</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U3</t>
+          <t>GBQ2U5</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Människan och den rörliga bilden</t>
+          <t>Kvalificerad filmdesign i transmedia</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -14206,14 +14206,14 @@
       </c>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U5</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U4</t>
+          <t>GBQ2U6</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Informationsfilmsproduktion</t>
+          <t>Projektplanering och användarperspektiv</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -14249,14 +14249,14 @@
       </c>
       <c r="I313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U5</t>
+          <t>GBQ2U7</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Kvalificerad filmdesign i transmedia</t>
+          <t>Tillämpad filmdesign 1</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -14292,14 +14292,14 @@
       </c>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U7</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U6</t>
+          <t>GBQ2U8</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Projektplanering och användarperspektiv</t>
+          <t>Den korta filmens berättarstruktur</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -14335,19 +14335,19 @@
       </c>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U8</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U7</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -14363,12 +14363,12 @@
       <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Tillämpad filmdesign 1</t>
+          <t>Kvinnor och gudinnor på gränsen till den äldsta förhistorien</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -14378,14 +14378,14 @@
       </c>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U8</t>
+          <t>GBQ2UB</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
+          <t>2022-02-07</t>
         </is>
       </c>
       <c r="E317" t="inlineStr"/>
@@ -14411,7 +14411,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Den korta filmens berättarstruktur</t>
+          <t>Introduktion till produktion av rörlig bild</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -14421,19 +14421,19 @@
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>GBQ2UN</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -14443,18 +14443,18 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Kvinnor och gudinnor på gränsen till den äldsta förhistorien</t>
+          <t>Filmanalys och gestaltning</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -14464,19 +14464,19 @@
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UN</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>GBQ2UB</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -14486,18 +14486,18 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Introduktion till produktion av rörlig bild</t>
+          <t>Naturbaserad turism</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -14507,19 +14507,19 @@
       </c>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>GBQ2UN</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -14529,18 +14529,18 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Filmanalys och gestaltning</t>
+          <t>Rektors ledning och organisering för utveckling av barns och elevers lärandemiljö</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -14550,19 +14550,19 @@
       </c>
       <c r="I320" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>APG27U</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -14572,18 +14572,18 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Naturbaserad turism</t>
+          <t>Utvärdering och verksamhetsutveckling i förskola och förskoleklass (varav 7,5 hp VFU)</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -14593,19 +14593,19 @@
       </c>
       <c r="I321" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>GLP2VT</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -14615,18 +14615,18 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Rektors ledning och organisering för utveckling av barns och elevers lärandemiljö</t>
+          <t>Produktionsprocesser inom musikproduktion</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -14636,14 +14636,14 @@
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>APG27U</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-03-15</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
@@ -14669,7 +14669,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Utvärdering och verksamhetsutveckling i förskola och förskoleklass (varav 7,5 hp VFU)</t>
+          <t>Professionellt lärarskap och skolutveckling (varav 10 hp VFU)</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -14679,19 +14679,19 @@
       </c>
       <c r="I323" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>GLP2VT</t>
+          <t>GBQ2WG</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -14701,18 +14701,18 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Produktionsprocesser inom musikproduktion</t>
+          <t>Audiovisuell information och etik</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -14722,19 +14722,19 @@
       </c>
       <c r="I324" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2VT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WG</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GBQ2WH</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -14744,18 +14744,18 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2022-03-15</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Professionellt lärarskap och skolutveckling (varav 10 hp VFU)</t>
+          <t>Tillämpad filmdesign 2</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -14765,14 +14765,14 @@
       </c>
       <c r="I325" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WG</t>
+          <t>GBQ2WJ</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Audiovisuell information och etik</t>
+          <t>Reklamfilmsproduktion</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -14808,14 +14808,14 @@
       </c>
       <c r="I326" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WJ</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WH</t>
+          <t>GBQ2WK</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Tillämpad filmdesign 2</t>
+          <t>Ljussättning och färgkorrigering inom filmdesign</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -14851,19 +14851,19 @@
       </c>
       <c r="I327" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WJ</t>
+          <t>GFÖ2WN</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -14873,18 +14873,18 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Reklamfilmsproduktion</t>
+          <t>Redovisning B</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -14894,19 +14894,19 @@
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ2WN</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WK</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -14916,18 +14916,18 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Ljussättning och färgkorrigering inom filmdesign</t>
+          <t>Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -14937,19 +14937,19 @@
       </c>
       <c r="I329" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>GFÖ2WN</t>
+          <t>GBQ2XC</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -14959,18 +14959,18 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Redovisning B</t>
+          <t>Manus för TV och film 3. Dialog i audiovisuella medier</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -14980,19 +14980,19 @@
       </c>
       <c r="I330" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ2WN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2XC</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>GBQ2XD</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -15002,18 +15002,18 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)</t>
+          <t>Ljudinspelning och ljudläggning inom filmdesign</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -15023,19 +15023,19 @@
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2XD</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>GBQ2XC</t>
+          <t>FPA222J</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -15045,18 +15045,18 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Manus för TV och film 3. Dialog i audiovisuella medier</t>
+          <t>Grundläggande statistik för utbildningsvetenskaplig forskning</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -15066,19 +15066,19 @@
       </c>
       <c r="I332" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2XC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>GBQ2XD</t>
+          <t>FPA222N</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -15088,18 +15088,18 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Ljudinspelning och ljudläggning inom filmdesign</t>
+          <t>Vetenskapliga metoder för forskning i pedagogiskt arbete</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -15109,19 +15109,19 @@
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2XD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>FPA222J</t>
+          <t>GRK323</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -15131,18 +15131,18 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Grundläggande statistik för utbildningsvetenskaplig forskning</t>
+          <t>Jerusalem som religiöst, historiskt och politiskt konfliktfylld plats. Berättelser ur ämnesdidaktiska perspektiv</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -15152,19 +15152,19 @@
       </c>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>FPA222N</t>
+          <t>GHI32G</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PEDAGARB</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -15174,18 +15174,18 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Vetenskapliga metoder för forskning i pedagogiskt arbete</t>
+          <t>Historia II med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -15195,19 +15195,19 @@
       </c>
       <c r="I335" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI32G</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>GRK323</t>
+          <t>GPA32D</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -15217,18 +15217,18 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Jerusalem som religiöst, historiskt och politiskt konfliktfylld plats. Berättelser ur ämnesdidaktiska perspektiv</t>
+          <t>Individuella lärprocesser och kompetensutveckling</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -15238,19 +15238,19 @@
       </c>
       <c r="I336" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>GHI32G</t>
+          <t>GLP33C</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -15260,18 +15260,18 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2023-02-24</t>
         </is>
       </c>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Historia II med didaktisk inriktning</t>
+          <t>Audiovisuell produktion för pedagogisk verksamhet</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -15281,19 +15281,19 @@
       </c>
       <c r="I337" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI32G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP33C</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>GPA32D</t>
+          <t>AS3001</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -15303,18 +15303,22 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr"/>
+          <t>2014-12-10</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Afrikanska studier</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Individuella lärprocesser och kompetensutveckling</t>
+          <t>Afrikanska studier: Utbildning och förändring i afrikanska samhällen</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -15324,19 +15328,19 @@
       </c>
       <c r="I338" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>GLP33C</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -15346,18 +15350,22 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr"/>
+          <t>2014-12-10</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Afrikanska studier</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Audiovisuell produktion för pedagogisk verksamhet</t>
+          <t>Afrikanska studier: Afrikanska samhällen i förändring</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -15367,14 +15375,14 @@
       </c>
       <c r="I339" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP33C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -15404,7 +15412,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Utbildning och förändring i afrikanska samhällen</t>
+          <t>Afrikanska studier: Religion och politik i afrikanska samhällen</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -15414,14 +15422,14 @@
       </c>
       <c r="I340" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>AS3004</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -15436,7 +15444,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
+          <t>2015-06-17</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -15451,7 +15459,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Afrikanska samhällen i förändring</t>
+          <t>Afrikanska studier: Forskningsprojektets planering</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -15461,19 +15469,19 @@
       </c>
       <c r="I341" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -15483,22 +15491,18 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
+          <t>2023-03-13</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Afrikanska studier</t>
+          <t>Sociologi</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Religion och politik i afrikanska samhällen</t>
+          <t>Sociologi III</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -15508,19 +15512,19 @@
       </c>
       <c r="I342" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>AS3004</t>
+          <t>GAB358</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -15530,22 +15534,18 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2015-06-17</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Afrikanska studier</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Afrikanska studier: Forskningsprojektets planering</t>
+          <t>Styrsystem och utveckling i socialtjänst/omsorg</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -15555,19 +15555,19 @@
       </c>
       <c r="I343" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB358</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>GPA353</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -15577,18 +15577,18 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Sociologi</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Sociologi III</t>
+          <t>Ledarskap</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -15598,19 +15598,19 @@
       </c>
       <c r="I344" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA353</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>GAB358</t>
+          <t>GPA354</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -15626,12 +15626,12 @@
       <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Personal och arbetsliv</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Styrsystem och utveckling i socialtjänst/omsorg</t>
+          <t>Arbetsrätt, avtal och förhandling</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -15641,14 +15641,14 @@
       </c>
       <c r="I345" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB358</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>GPA353</t>
+          <t>GPA357</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Ledarskap</t>
+          <t>Praktik för personalvetare</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -15684,19 +15684,19 @@
       </c>
       <c r="I346" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA353</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA357</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>GPA354</t>
+          <t>GLP359</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -15706,18 +15706,18 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Arbetsrätt, avtal och förhandling</t>
+          <t>Dansmusikhistoria och klubbkultur 1: DJ-kulturens utveckling 1970-2000</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -15727,19 +15727,19 @@
       </c>
       <c r="I347" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>GPA357</t>
+          <t>GFÖ35J</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -15749,18 +15749,18 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Personal och arbetsliv</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Praktik för personalvetare</t>
+          <t>Turismmarknadsföring</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -15770,19 +15770,19 @@
       </c>
       <c r="I348" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA357</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ35J</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>GLP359</t>
+          <t>GBQ35K</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -15792,18 +15792,18 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Dansmusikhistoria och klubbkultur 1: DJ-kulturens utveckling 1970-2000</t>
+          <t>Berätta med film om kulturarv och historia</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -15813,19 +15813,19 @@
       </c>
       <c r="I349" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ35K</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>GFÖ35J</t>
+          <t>GEU35L</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -15835,18 +15835,18 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Turismmarknadsföring</t>
+          <t>Projektledning I</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -15856,19 +15856,19 @@
       </c>
       <c r="I350" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ35J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35L</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>GBQ35K</t>
+          <t>GEU35M</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -15878,18 +15878,18 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Berätta med film om kulturarv och historia</t>
+          <t>Entreprenörskap - villkor och särart</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -15899,14 +15899,14 @@
       </c>
       <c r="I351" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ35K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35M</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>GEU35L</t>
+          <t>GEU35N</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Projektledning I</t>
+          <t>Projektledning II</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -15942,19 +15942,19 @@
       </c>
       <c r="I352" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35N</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>GEU35M</t>
+          <t>GBQ36D</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -15964,18 +15964,18 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Entreprenörskap - villkor och särart</t>
+          <t>Kvalificerad filmproduktion</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -15985,19 +15985,19 @@
       </c>
       <c r="I353" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36D</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>GEU35N</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -16007,18 +16007,18 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Projektledning II</t>
+          <t>Didaktik och läroplansteori - KPU</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -16028,19 +16028,19 @@
       </c>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU35N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>GBQ36D</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -16050,18 +16050,18 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Kvalificerad filmproduktion</t>
+          <t>Didaktik och läroplansteori</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -16071,19 +16071,19 @@
       </c>
       <c r="I355" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>ARK29H</t>
+          <t>GBQ36K</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -16093,18 +16093,18 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Religionsvetenskaplig litteraturkurs</t>
+          <t>Flerkameraproduktion, fördjupning</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -16114,19 +16114,19 @@
       </c>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>AHI29P</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -16136,18 +16136,18 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Didaktik och läroplansteori - KPU</t>
+          <t>Examensarbete, magisterexamen i historia</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -16157,19 +16157,19 @@
       </c>
       <c r="I357" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29P</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GHI37M</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -16179,18 +16179,18 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Didaktik och läroplansteori</t>
+          <t>De nationella minoriteternas samhällshistoria</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -16200,19 +16200,19 @@
       </c>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI37M</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>GBQ36K</t>
+          <t>GFI37Z</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -16222,18 +16222,18 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-12-07</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Flerkameraproduktion, fördjupning</t>
+          <t>Gud och bevisen: filosofiska argument för och mot Guds existens</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -16243,14 +16243,14 @@
       </c>
       <c r="I359" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>GHI38Q</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Historievetenskaplig litteraturkurs</t>
+          <t>Global miljöhistoria</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -16286,19 +16286,19 @@
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI38Q</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>AHI29R</t>
+          <t>GBQ38X</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -16308,18 +16308,18 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Historievetenskapens teori och metod</t>
+          <t>Fortsätt berätta med film om kulturarv och historia</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -16329,19 +16329,19 @@
       </c>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>GHI37M</t>
+          <t>GEU38C</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -16351,18 +16351,18 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Entreprenörskap och innovationsteknik</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>De nationella minoriteternas samhällshistoria</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -16372,19 +16372,19 @@
       </c>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI37M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU38C</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>GFI37Z</t>
+          <t>APG2AA</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -16394,18 +16394,18 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2023-12-07</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Gud och bevisen: filosofiska argument för och mot Guds existens</t>
+          <t>Lärarskicklighet - utveckling av lärarskicklighet i förskola och skola utifrån forskning</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -16415,19 +16415,19 @@
       </c>
       <c r="I363" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>GHI38Q</t>
+          <t>GFÖ39A</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -16437,18 +16437,18 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Global miljöhistoria</t>
+          <t>Sport Management III</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -16458,14 +16458,14 @@
       </c>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI38Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ39A</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>GBQ38X</t>
+          <t>GBQ3A5</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Fortsätt berätta med film om kulturarv och historia</t>
+          <t>Grunderna i filmproduktion</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -16501,19 +16501,19 @@
       </c>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A5</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>GEU38C</t>
+          <t>GBQ3A6</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -16523,18 +16523,18 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Entreprenörskap och innovationsteknik</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>Konceptutveckling för korta filmer</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -16544,19 +16544,19 @@
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU38C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>APG2AA</t>
+          <t>GBQ3A7</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -16566,18 +16566,18 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Lärarskicklighet - utveckling av lärarskicklighet i förskola och skola utifrån forskning</t>
+          <t>Star Wars: Film, myter och världar</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -16587,19 +16587,19 @@
       </c>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>GFÖ39A</t>
+          <t>GBQ3A8</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>FÖA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -16609,18 +16609,18 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Företagsekonomi</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Sport Management III</t>
+          <t>Kreativt skrivande</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -16630,14 +16630,14 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFÖ39A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A8</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A5</t>
+          <t>GBQ3A9</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Grunderna i filmproduktion</t>
+          <t>Introduktion till att skriva filmadaption</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -16673,14 +16673,14 @@
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A9</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A6</t>
+          <t>GBQ3AA</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Konceptutveckling för korta filmer</t>
+          <t>Filmhistoria: En introduktion</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -16716,19 +16716,19 @@
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A7</t>
+          <t>GTR3A4</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -16744,12 +16744,12 @@
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Star Wars: Film, myter och världar</t>
+          <t>Kvantitativ metod</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -16759,19 +16759,19 @@
       </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A9</t>
+          <t>APG2AB</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -16781,18 +16781,18 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Introduktion till att skriva filmadaption</t>
+          <t>Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -16802,19 +16802,19 @@
       </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AB</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AA</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -16824,18 +16824,18 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Filmhistoria: En introduktion</t>
+          <t>Rektors pedagogiska ledarskap med fokus på förskolans utbildningsuppdrag</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -16845,19 +16845,19 @@
       </c>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>GTR3A4</t>
+          <t>GPG3AG</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -16867,18 +16867,18 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Kvantitativ metod</t>
+          <t>Verksamhetsförlagd utbildning 2 för ämneslärare årskurs 7–9 - AIL</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -16888,19 +16888,19 @@
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>APG2AB</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -16910,18 +16910,18 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Ljud- och musikproduktion</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL</t>
+          <t>Hårdrock och metal: musikproduktion, kultur och kreativa konventioner</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -16931,19 +16931,19 @@
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>GAB3AK</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -16953,18 +16953,18 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Rektors pedagogiska ledarskap med fokus på förskolans utbildningsuppdrag</t>
+          <t>Kommunal styrning och förändringsarbete</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -16974,19 +16974,19 @@
       </c>
       <c r="I376" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AK</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>GPG3AF</t>
+          <t>GAB3AL</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -16996,18 +16996,18 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Specialpedagogik och ett läraruppdrag i förändring för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Ledarskapets juridik</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -17017,19 +17017,19 @@
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AL</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>GPG3AG</t>
+          <t>GPE3AJ</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -17039,18 +17039,18 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Pedagogik</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 2 för ämneslärare årskurs 7–9 - AIL</t>
+          <t>Att leda kollegiala lärprocesser i förskola och skola</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -17060,14 +17060,14 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>GLP3AR</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -17082,7 +17082,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
@@ -17093,7 +17093,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Hårdrock och metal: musikproduktion, kultur och kreativa konventioner</t>
+          <t>Ljud- och musikproduktion med Pro Tools</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -17103,19 +17103,19 @@
       </c>
       <c r="I379" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>GAB3AK</t>
+          <t>GBQ3AV</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -17125,18 +17125,18 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Kommunal styrning och förändringsarbete</t>
+          <t>Content för sociala medier</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -17146,19 +17146,19 @@
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>GAB3AL</t>
+          <t>GBQ3AW</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -17168,18 +17168,18 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Arbetsvetenskap</t>
+          <t>Bildproduktion</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Ledarskapets juridik</t>
+          <t>Explainers med rörlig grafik</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -17189,19 +17189,19 @@
       </c>
       <c r="I381" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>GPE3AJ</t>
+          <t>GTR3B6</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -17211,18 +17211,18 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Pedagogik</t>
+          <t>Turismvetenskap</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Att leda kollegiala lärprocesser i förskola och skola</t>
+          <t>Sälenfjällen - Platsen och besöksnäringen</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -17232,19 +17232,19 @@
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>GLP3AR</t>
+          <t>GNA3B7</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -17254,18 +17254,18 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion</t>
+          <t>Nationalekonomi</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Ljud- och musikproduktion med Pro Tools</t>
+          <t>Mikroekonomi, introduktion</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -17275,19 +17275,19 @@
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B7</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AV</t>
+          <t>GBP3BB</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -17297,18 +17297,18 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Content för sociala medier</t>
+          <t>Fotografiskt bildskapande A</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -17318,19 +17318,19 @@
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BB</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AW</t>
+          <t>GBP3BC</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -17340,18 +17340,18 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Explainers med rörlig grafik</t>
+          <t>Fotografiskt bildskapande B</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -17361,19 +17361,19 @@
       </c>
       <c r="I385" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BC</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>GTR3B6</t>
+          <t>GPG3BD</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -17383,18 +17383,18 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Turismvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Sälenfjällen - Platsen och besöksnäringen</t>
+          <t>Introduktion till läraryrket</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -17404,19 +17404,19 @@
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>GNA3B7</t>
+          <t>GFI3BU</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -17426,18 +17426,18 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Nationalekonomi</t>
+          <t>Filosofi</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Mikroekonomi, introduktion</t>
+          <t>Introduktion till existentialismen</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -17447,19 +17447,19 @@
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>GBP3BB</t>
+          <t>GPG3CN</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -17469,18 +17469,18 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Fotografiskt bildskapande A</t>
+          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -17490,19 +17490,19 @@
       </c>
       <c r="I388" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>GBP3BC</t>
+          <t>GRK3CQ</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -17512,18 +17512,18 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Religionsvetenskap</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Fotografiskt bildskapande B</t>
+          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -17533,19 +17533,19 @@
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP3BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>GPG3BD</t>
+          <t>GMN3EZ</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -17555,18 +17555,18 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Introduktion till läraryrket</t>
+          <t>Kandidatexamensarbete i Medieproduktion</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -17576,19 +17576,19 @@
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>GFI3BU</t>
+          <t>GMN3EX</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -17598,18 +17598,18 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Filosofi</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Introduktion till existentialismen</t>
+          <t>Alternativa gestaltningsformer</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -17619,19 +17619,19 @@
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>ABQ2AM</t>
+          <t>GMN3EY</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -17641,18 +17641,18 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Kreativ kodning</t>
+          <t>Vetenskapsteori och metod i Medieproduktion</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -17662,19 +17662,19 @@
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EY</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>GPG3CN</t>
+          <t>GMN3F2</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -17684,18 +17684,18 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Medieproduktion</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel - inriktning pedagogiskt arbete</t>
+          <t>Exponeringsprojekt inom Medieproduktion</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -17705,19 +17705,19 @@
       </c>
       <c r="I393" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>GHI3CP</t>
+          <t>APG2BF</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -17727,18 +17727,18 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel – inriktning historiedidaktik</t>
+          <t>Att främja en professionsdriven verksamhetsutveckling i förskola, skola och fritidshem</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -17748,19 +17748,19 @@
       </c>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>GRK3CQ</t>
+          <t>APG2BK</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -17770,18 +17770,18 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Religionsvetenskap</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Undervisning och lärande genom rollspel – inriktning religionsdidaktik</t>
+          <t>Verksamhetsförlagd utbildning 3 - VAL</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -17791,19 +17791,19 @@
       </c>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>GMN3E2</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -17813,18 +17813,18 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Dramaturgi, manusskrivande och medieproduktionens villkor</t>
+          <t>Introduktion till studier i program - VAL</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -17834,19 +17834,19 @@
       </c>
       <c r="I396" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>GMN3EZ</t>
+          <t>GPG3FS</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -17856,18 +17856,18 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Kandidatexamensarbete i Medieproduktion</t>
+          <t>Verksamhetsförlagd utbildning 1 - VAL</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -17877,19 +17877,19 @@
       </c>
       <c r="I397" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>GMN3EX</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -17899,18 +17899,18 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Alternativa gestaltningsformer</t>
+          <t>Verksamhetsförlagd utbildning 2 - VAL</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -17920,14 +17920,14 @@
       </c>
       <c r="I398" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>GMN3EY</t>
+          <t>GMN3F3</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
@@ -17953,7 +17953,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Vetenskapsteori och metod i Medieproduktion</t>
+          <t>Verksamhetsförlagd utbildning inom medieproduktion</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -17963,19 +17963,19 @@
       </c>
       <c r="I399" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F3</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>GMN3F2</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -17985,18 +17985,18 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Exponeringsprojekt inom Medieproduktion</t>
+          <t>Mentorsutbildning för en kvalitativ introduktionsperiod</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -18006,19 +18006,19 @@
       </c>
       <c r="I400" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>GBQ3FG</t>
+          <t>GPG3JP</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -18028,18 +18028,18 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Bildproduktion</t>
+          <t>Pedagogiskt arbete</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Kreativt skrivande</t>
+          <t>Interkulturell och inkluderande undervisning i globala sammanhang</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -18049,19 +18049,19 @@
       </c>
       <c r="I401" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>APG2BF</t>
+          <t>GKG3KD</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -18071,18 +18071,18 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Kulturgeografi</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Att främja en professionsdriven verksamhetsutveckling i förskola, skola och fritidshem</t>
+          <t>Geografiska Informationssystem (GIS): Introduktion</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -18092,19 +18092,19 @@
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3KD</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>APG2BK</t>
+          <t>GKG3KE</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -18114,18 +18114,18 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Kulturgeografi</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 3 - VAL</t>
+          <t>Geografiska Informationssystem (GIS): Introduktion till GIS-analyser</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -18135,19 +18135,19 @@
       </c>
       <c r="I403" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3KE</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GKG3KF</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -18157,18 +18157,18 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Kulturgeografi</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Introduktion till studier i program - VAL</t>
+          <t>Geografiska Informationssystem (GIS): Rumslig analys och statistik</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -18178,19 +18178,19 @@
       </c>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3KF</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>GPG3FS</t>
+          <t>AAB2CX</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -18200,18 +18200,18 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Arbetsvetenskap</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 1 - VAL</t>
+          <t>Ledarskap för hållbar organisationsförändring</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -18221,19 +18221,19 @@
       </c>
       <c r="I405" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AAB2CX</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>GPG3FT</t>
+          <t>AFÖ2CV</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -18243,18 +18243,18 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning 2 - VAL</t>
+          <t>Organisationsteori och organisationsanalys</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -18264,19 +18264,19 @@
       </c>
       <c r="I406" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFÖ2CV</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>GMN3F3</t>
+          <t>AFÖ2CW</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -18286,18 +18286,18 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr">
         <is>
-          <t>Medieproduktion</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Verksamhetsförlagd utbildning inom medieproduktion</t>
+          <t>Strategiskt management och hållbarhet</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -18307,19 +18307,19 @@
       </c>
       <c r="I407" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFÖ2CW</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>AFÖ2CY</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>FÖA</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -18329,18 +18329,18 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E408" t="inlineStr"/>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Pedagogiskt arbete</t>
+          <t>Företagsekonomi</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Mentorsutbildning för en kvalitativ introduktionsperiod</t>
+          <t>Human Resource Management och organisatorisk prestation</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -18350,184 +18350,12 @@
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" s="2" t="inlineStr">
-        <is>
-          <t>GPG3JP</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>PGA</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr">
-        <is>
-          <t>Pedagogiskt arbete</t>
-        </is>
-      </c>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>Interkulturell och inkluderande undervisning i globala sammanhang</t>
-        </is>
-      </c>
-      <c r="H409" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I409" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" s="2" t="inlineStr">
-        <is>
-          <t>GKG3KD</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>KGA</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>Kulturgeografi</t>
-        </is>
-      </c>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>Geografiska Informationssystem (GIS): Introduktion</t>
-        </is>
-      </c>
-      <c r="H410" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I410" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3KD</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" s="2" t="inlineStr">
-        <is>
-          <t>GKG3KE</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>KGA</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>Kulturgeografi</t>
-        </is>
-      </c>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>Geografiska Informationssystem (GIS): Introduktion till GIS-analyser</t>
-        </is>
-      </c>
-      <c r="H411" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I411" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3KE</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" s="2" t="inlineStr">
-        <is>
-          <t>GKG3KF</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>KGA</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>IKS</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>Kulturgeografi</t>
-        </is>
-      </c>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>Geografiska Informationssystem (GIS): Rumslig analys och statistik</t>
-        </is>
-      </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I412" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3KF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFÖ2CY</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I412"/>
+  <autoFilter ref="A1:I408"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -19343,14 +19171,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I407" r:id="rId812"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A408" r:id="rId813"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I408" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A409" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I409" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A410" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I410" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A411" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I411" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A412" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I412" r:id="rId822"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
